--- a/input/timetable/Лингвистика_.xlsx
+++ b/input/timetable/Лингвистика_.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="208">
   <si>
     <t>пара</t>
   </si>
@@ -231,9 +231,6 @@
   </si>
   <si>
     <t>Педагогическая антропология (лек)/(пр), К408</t>
-  </si>
-  <si>
-    <t>Иностр. язык (англ. язык), п/г 2, К406</t>
   </si>
   <si>
     <t>Практ. курс перевода англ. языка, п/г 2, К406</t>
@@ -378,9 +375,6 @@
     <t>Основы проектной деятельности (лек 16 ч)</t>
   </si>
   <si>
-    <t>Теория и методика преподавания иностранных языков (лек)/(пр), К408</t>
-  </si>
-  <si>
     <t>ФТД: Практикум по культуре речевого общения  франц. языка, п/г 2, К407</t>
   </si>
   <si>
@@ -471,9 +465,6 @@
     <t>Практическая грамматика англ. языка, п/г 2, К406</t>
   </si>
   <si>
-    <t>Практическая грамматика англ. языка, п/г 1, К405</t>
-  </si>
-  <si>
     <t>День самостоятельной работы</t>
   </si>
   <si>
@@ -552,11 +543,6 @@
     <t>Практикум по культуре речевого общения немецкого языка, п/г 2, К409</t>
   </si>
   <si>
-    <t xml:space="preserve">Практикум по культуре речевого общения немецкого языка, п/г 2, К409
-Практикум по культуре речевого общения ВИЯ, п/г 2
-</t>
-  </si>
-  <si>
     <t>Основы теории немецкого языка (лек), К408</t>
   </si>
   <si>
@@ -588,9 +574,6 @@
   </si>
   <si>
     <t>Работа в команде (пр), К426// Возрастная психология (начальная школа) (пр), К312</t>
-  </si>
-  <si>
-    <t>// Психология инклюзивного общества (пр), ЭОиДОТ</t>
   </si>
   <si>
     <t xml:space="preserve">Учебная практика, переводческая практика, К304// </t>
@@ -647,6 +630,25 @@
   </si>
   <si>
     <t>Инстр. язык (нем. язык), п/г 2, К313</t>
+  </si>
+  <si>
+    <t>// Психология инклюзивного общества (пр), К408</t>
+  </si>
+  <si>
+    <t>Психология инклюзивного общества (пр), К408//</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Практикум по культуре речевого общения немецкого языка, п/г 2, К409
+</t>
+  </si>
+  <si>
+    <t>Теория и методика преподавания иностранных языков (лек)/(пр), К413</t>
+  </si>
+  <si>
+    <t>Практическая грамматика англ. языка, п/г 1, К406</t>
+  </si>
+  <si>
+    <t>Иностр. язык (англ. язык), п/г 2, К405</t>
   </si>
 </sst>
 </file>
@@ -1968,11 +1970,211 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1989,268 +2191,86 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2264,34 +2284,61 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2306,15 +2353,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2323,15 +2361,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2384,124 +2413,118 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2510,50 +2533,31 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2561,136 +2565,30 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2703,46 +2601,198 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2750,155 +2800,23 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2906,23 +2824,17 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2930,10 +2842,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2954,41 +2866,131 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3331,13 +3333,13 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>11</v>
@@ -3360,11 +3362,11 @@
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G4" s="1"/>
       <c r="L4" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -3390,7 +3392,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="9" t="s">
@@ -3403,7 +3405,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="9" t="s">
@@ -3417,10 +3419,10 @@
       <c r="A7" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="222" t="s">
+      <c r="C7" s="198" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="222"/>
+      <c r="D7" s="198"/>
       <c r="E7" s="9">
         <v>1</v>
       </c>
@@ -3430,10 +3432,10 @@
       <c r="G7" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="213" t="s">
+      <c r="I7" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="213"/>
+      <c r="J7" s="184"/>
       <c r="K7" s="9">
         <v>1</v>
       </c>
@@ -3450,7 +3452,7 @@
       </c>
       <c r="D8" s="47"/>
       <c r="E8" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>7</v>
@@ -3463,7 +3465,7 @@
       </c>
       <c r="J8" s="47"/>
       <c r="K8" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L8" s="15" t="s">
         <v>7</v>
@@ -3473,19 +3475,19 @@
       <c r="A9" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="214" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" s="214"/>
-      <c r="E9" s="214"/>
+      <c r="C9" s="185" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="185"/>
+      <c r="E9" s="185"/>
       <c r="F9" s="15"/>
       <c r="G9" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="214" t="s">
-        <v>101</v>
-      </c>
-      <c r="J9" s="214"/>
+      <c r="I9" s="185" t="s">
+        <v>100</v>
+      </c>
+      <c r="J9" s="185"/>
       <c r="K9" s="14"/>
       <c r="L9" s="15"/>
     </row>
@@ -3522,10 +3524,10 @@
       <c r="B11" s="91">
         <v>1</v>
       </c>
-      <c r="C11" s="223"/>
-      <c r="D11" s="224"/>
-      <c r="E11" s="224"/>
-      <c r="F11" s="225"/>
+      <c r="C11" s="199"/>
+      <c r="D11" s="200"/>
+      <c r="E11" s="200"/>
+      <c r="F11" s="201"/>
       <c r="G11" s="22" t="s">
         <v>21</v>
       </c>
@@ -3534,7 +3536,7 @@
       </c>
       <c r="I11" s="119"/>
       <c r="J11" s="143" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K11" s="120"/>
       <c r="L11" s="121"/>
@@ -3544,27 +3546,27 @@
       <c r="B12" s="92">
         <v>2</v>
       </c>
-      <c r="C12" s="180" t="s">
-        <v>198</v>
-      </c>
-      <c r="D12" s="181"/>
-      <c r="E12" s="178" t="s">
-        <v>125</v>
-      </c>
-      <c r="F12" s="179"/>
+      <c r="C12" s="202" t="s">
+        <v>193</v>
+      </c>
+      <c r="D12" s="203"/>
+      <c r="E12" s="225" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" s="221"/>
       <c r="G12" s="23"/>
       <c r="H12" s="92">
         <v>2</v>
       </c>
       <c r="I12" s="116"/>
       <c r="J12" s="146" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K12" s="145" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L12" s="144" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3572,25 +3574,25 @@
       <c r="B13" s="92">
         <v>3</v>
       </c>
-      <c r="C13" s="180" t="s">
+      <c r="C13" s="202" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="181"/>
-      <c r="E13" s="232" t="s">
+      <c r="D13" s="203"/>
+      <c r="E13" s="210" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="233"/>
+      <c r="F13" s="211"/>
       <c r="G13" s="23"/>
       <c r="H13" s="92">
         <v>3</v>
       </c>
       <c r="I13" s="142" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J13" s="122"/>
       <c r="K13" s="129"/>
       <c r="L13" s="144" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -3598,16 +3600,16 @@
       <c r="B14" s="93">
         <v>4</v>
       </c>
-      <c r="C14" s="226"/>
-      <c r="D14" s="227"/>
-      <c r="E14" s="227"/>
-      <c r="F14" s="228"/>
+      <c r="C14" s="204"/>
+      <c r="D14" s="205"/>
+      <c r="E14" s="205"/>
+      <c r="F14" s="206"/>
       <c r="G14" s="23"/>
       <c r="H14" s="92">
         <v>4</v>
       </c>
       <c r="I14" s="147" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J14" s="117"/>
       <c r="K14" s="117"/>
@@ -3620,12 +3622,12 @@
       <c r="B15" s="25">
         <v>1</v>
       </c>
-      <c r="C15" s="219" t="s">
+      <c r="C15" s="192" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="220"/>
-      <c r="E15" s="220"/>
-      <c r="F15" s="221"/>
+      <c r="D15" s="193"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="194"/>
       <c r="G15" s="22" t="s">
         <v>22</v>
       </c>
@@ -3633,11 +3635,11 @@
         <v>1</v>
       </c>
       <c r="I15" s="155" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J15" s="128"/>
       <c r="K15" s="148" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L15" s="149"/>
     </row>
@@ -3646,47 +3648,47 @@
       <c r="B16" s="28">
         <v>2</v>
       </c>
-      <c r="C16" s="180" t="s">
-        <v>201</v>
-      </c>
-      <c r="D16" s="181"/>
-      <c r="E16" s="178" t="s">
+      <c r="C16" s="202" t="s">
+        <v>196</v>
+      </c>
+      <c r="D16" s="203"/>
+      <c r="E16" s="225" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="179"/>
+      <c r="F16" s="221"/>
       <c r="G16" s="27"/>
       <c r="H16" s="28">
         <v>2</v>
       </c>
-      <c r="I16" s="203" t="s">
+      <c r="I16" s="195" t="s">
         <v>60</v>
       </c>
-      <c r="J16" s="204"/>
-      <c r="K16" s="204"/>
-      <c r="L16" s="205"/>
+      <c r="J16" s="196"/>
+      <c r="K16" s="196"/>
+      <c r="L16" s="197"/>
     </row>
     <row r="17" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="27"/>
       <c r="B17" s="28">
         <v>3</v>
       </c>
-      <c r="C17" s="234"/>
-      <c r="D17" s="235"/>
-      <c r="E17" s="178" t="s">
+      <c r="C17" s="212"/>
+      <c r="D17" s="213"/>
+      <c r="E17" s="225" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="179"/>
+      <c r="F17" s="221"/>
       <c r="G17" s="27"/>
       <c r="H17" s="28">
         <v>3</v>
       </c>
       <c r="I17" s="126"/>
       <c r="J17" s="134" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K17" s="129"/>
       <c r="L17" s="156" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -3694,18 +3696,18 @@
       <c r="B18" s="30">
         <v>4</v>
       </c>
-      <c r="C18" s="229"/>
-      <c r="D18" s="230"/>
-      <c r="E18" s="230"/>
-      <c r="F18" s="231"/>
+      <c r="C18" s="207"/>
+      <c r="D18" s="208"/>
+      <c r="E18" s="208"/>
+      <c r="F18" s="209"/>
       <c r="G18" s="29"/>
       <c r="H18" s="30">
         <v>4</v>
       </c>
-      <c r="I18" s="216"/>
-      <c r="J18" s="217"/>
-      <c r="K18" s="217"/>
-      <c r="L18" s="218"/>
+      <c r="I18" s="189"/>
+      <c r="J18" s="190"/>
+      <c r="K18" s="190"/>
+      <c r="L18" s="191"/>
     </row>
     <row r="19" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="22" t="s">
@@ -3714,46 +3716,46 @@
       <c r="B19" s="25">
         <v>2</v>
       </c>
-      <c r="C19" s="182" t="s">
+      <c r="C19" s="186" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="183"/>
-      <c r="E19" s="183"/>
-      <c r="F19" s="215"/>
+      <c r="D19" s="187"/>
+      <c r="E19" s="187"/>
+      <c r="F19" s="188"/>
       <c r="G19" s="22" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="91">
         <v>1</v>
       </c>
-      <c r="I19" s="182" t="s">
+      <c r="I19" s="186" t="s">
         <v>28</v>
       </c>
-      <c r="J19" s="183"/>
-      <c r="K19" s="183"/>
-      <c r="L19" s="215"/>
+      <c r="J19" s="187"/>
+      <c r="K19" s="187"/>
+      <c r="L19" s="188"/>
     </row>
     <row r="20" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="31"/>
       <c r="B20" s="28">
         <v>4</v>
       </c>
-      <c r="C20" s="190" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" s="191"/>
-      <c r="E20" s="191"/>
-      <c r="F20" s="192"/>
+      <c r="C20" s="172" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="173"/>
+      <c r="E20" s="173"/>
+      <c r="F20" s="174"/>
       <c r="G20" s="32"/>
       <c r="H20" s="94">
         <v>3</v>
       </c>
       <c r="I20" s="150"/>
       <c r="J20" s="146" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K20" s="146" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L20" s="154"/>
     </row>
@@ -3762,42 +3764,42 @@
       <c r="B21" s="28">
         <v>5</v>
       </c>
-      <c r="C21" s="180" t="s">
+      <c r="C21" s="202" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="209"/>
-      <c r="E21" s="209"/>
-      <c r="F21" s="179"/>
+      <c r="D21" s="220"/>
+      <c r="E21" s="220"/>
+      <c r="F21" s="221"/>
       <c r="G21" s="23"/>
       <c r="H21" s="92">
         <v>4</v>
       </c>
-      <c r="I21" s="203" t="s">
+      <c r="I21" s="195" t="s">
         <v>62</v>
       </c>
-      <c r="J21" s="204"/>
-      <c r="K21" s="204"/>
-      <c r="L21" s="205"/>
+      <c r="J21" s="196"/>
+      <c r="K21" s="196"/>
+      <c r="L21" s="197"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="34"/>
       <c r="B22" s="30">
         <v>6</v>
       </c>
-      <c r="C22" s="210"/>
-      <c r="D22" s="211"/>
-      <c r="E22" s="211"/>
-      <c r="F22" s="212"/>
+      <c r="C22" s="222"/>
+      <c r="D22" s="223"/>
+      <c r="E22" s="223"/>
+      <c r="F22" s="224"/>
       <c r="G22" s="24"/>
       <c r="H22" s="93">
         <v>5</v>
       </c>
-      <c r="I22" s="196" t="s">
-        <v>124</v>
-      </c>
-      <c r="J22" s="197"/>
-      <c r="K22" s="197"/>
-      <c r="L22" s="198"/>
+      <c r="I22" s="214" t="s">
+        <v>122</v>
+      </c>
+      <c r="J22" s="215"/>
+      <c r="K22" s="215"/>
+      <c r="L22" s="216"/>
     </row>
     <row r="23" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="22" t="s">
@@ -3806,10 +3808,10 @@
       <c r="B23" s="26">
         <v>1</v>
       </c>
-      <c r="C23" s="186"/>
-      <c r="D23" s="187"/>
-      <c r="E23" s="188"/>
-      <c r="F23" s="189"/>
+      <c r="C23" s="229"/>
+      <c r="D23" s="230"/>
+      <c r="E23" s="231"/>
+      <c r="F23" s="232"/>
       <c r="G23" s="22" t="s">
         <v>24</v>
       </c>
@@ -3819,7 +3821,7 @@
       <c r="I23" s="135"/>
       <c r="J23" s="136"/>
       <c r="K23" s="139" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L23" s="138"/>
     </row>
@@ -3828,27 +3830,27 @@
       <c r="B24" s="28">
         <v>2</v>
       </c>
-      <c r="C24" s="201" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" s="202"/>
-      <c r="E24" s="202" t="s">
-        <v>192</v>
-      </c>
-      <c r="F24" s="245"/>
+      <c r="C24" s="166" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="167"/>
+      <c r="E24" s="167" t="s">
+        <v>187</v>
+      </c>
+      <c r="F24" s="168"/>
       <c r="G24" s="27"/>
       <c r="H24" s="28">
         <v>2</v>
       </c>
       <c r="I24" s="131" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J24" s="130"/>
       <c r="K24" s="134" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L24" s="141" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -3856,27 +3858,27 @@
       <c r="B25" s="28">
         <v>3</v>
       </c>
-      <c r="C25" s="201" t="s">
-        <v>193</v>
-      </c>
-      <c r="D25" s="202"/>
-      <c r="E25" s="207" t="s">
+      <c r="C25" s="166" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="167"/>
+      <c r="E25" s="176" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="208"/>
+      <c r="F25" s="179"/>
       <c r="G25" s="27"/>
       <c r="H25" s="28">
         <v>3</v>
       </c>
       <c r="I25" s="131" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J25" s="134" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K25" s="130"/>
       <c r="L25" s="141" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -3884,10 +3886,10 @@
       <c r="B26" s="36">
         <v>4</v>
       </c>
-      <c r="C26" s="206"/>
-      <c r="D26" s="199"/>
-      <c r="E26" s="199"/>
-      <c r="F26" s="200"/>
+      <c r="C26" s="219"/>
+      <c r="D26" s="217"/>
+      <c r="E26" s="217"/>
+      <c r="F26" s="218"/>
       <c r="G26" s="35"/>
       <c r="H26" s="36">
         <v>4</v>
@@ -3904,12 +3906,12 @@
       <c r="B27" s="91">
         <v>1</v>
       </c>
-      <c r="C27" s="182" t="s">
+      <c r="C27" s="186" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="183"/>
-      <c r="E27" s="184"/>
-      <c r="F27" s="185"/>
+      <c r="D27" s="187"/>
+      <c r="E27" s="227"/>
+      <c r="F27" s="228"/>
       <c r="G27" s="22" t="s">
         <v>25</v>
       </c>
@@ -3917,7 +3919,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="151" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="J27" s="132"/>
       <c r="K27" s="132"/>
@@ -3928,24 +3930,24 @@
       <c r="B28" s="92">
         <v>2</v>
       </c>
-      <c r="C28" s="249" t="s">
-        <v>198</v>
-      </c>
-      <c r="D28" s="207"/>
-      <c r="E28" s="207" t="s">
+      <c r="C28" s="175" t="s">
+        <v>193</v>
+      </c>
+      <c r="D28" s="176"/>
+      <c r="E28" s="176" t="s">
         <v>61</v>
       </c>
-      <c r="F28" s="208"/>
+      <c r="F28" s="179"/>
       <c r="G28" s="37"/>
       <c r="H28" s="92">
         <v>2</v>
       </c>
       <c r="I28" s="142" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J28" s="122"/>
       <c r="K28" s="145" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="L28" s="123"/>
     </row>
@@ -3954,23 +3956,23 @@
       <c r="B29" s="95">
         <v>3</v>
       </c>
-      <c r="C29" s="250"/>
-      <c r="D29" s="251"/>
-      <c r="E29" s="251"/>
-      <c r="F29" s="252"/>
+      <c r="C29" s="177"/>
+      <c r="D29" s="178"/>
+      <c r="E29" s="178"/>
+      <c r="F29" s="180"/>
       <c r="G29" s="38"/>
       <c r="H29" s="95">
         <v>3</v>
       </c>
       <c r="I29" s="126"/>
       <c r="J29" s="145" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K29" s="145" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L29" s="144" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -3978,21 +3980,21 @@
       <c r="B30" s="95">
         <v>4</v>
       </c>
-      <c r="C30" s="246"/>
-      <c r="D30" s="247"/>
-      <c r="E30" s="247"/>
-      <c r="F30" s="248"/>
+      <c r="C30" s="169"/>
+      <c r="D30" s="170"/>
+      <c r="E30" s="170"/>
+      <c r="F30" s="171"/>
       <c r="G30" s="39"/>
       <c r="H30" s="93">
         <v>4</v>
       </c>
       <c r="I30" s="124"/>
       <c r="J30" s="153" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K30" s="125"/>
       <c r="L30" s="152" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
@@ -4002,186 +4004,186 @@
       <c r="B31" s="26">
         <v>3</v>
       </c>
-      <c r="C31" s="239" t="s">
+      <c r="C31" s="160" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="E31" s="240"/>
-      <c r="F31" s="241"/>
+      <c r="D31" s="161"/>
+      <c r="E31" s="161"/>
+      <c r="F31" s="162"/>
       <c r="G31" s="40" t="s">
         <v>26</v>
       </c>
       <c r="H31" s="81">
         <v>3</v>
       </c>
-      <c r="I31" s="242"/>
-      <c r="J31" s="243"/>
-      <c r="K31" s="243"/>
-      <c r="L31" s="244"/>
+      <c r="I31" s="163"/>
+      <c r="J31" s="164"/>
+      <c r="K31" s="164"/>
+      <c r="L31" s="165"/>
     </row>
     <row r="32" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="77"/>
       <c r="B32" s="28">
         <v>4</v>
       </c>
-      <c r="C32" s="253"/>
-      <c r="D32" s="254"/>
-      <c r="E32" s="254"/>
-      <c r="F32" s="255"/>
+      <c r="C32" s="181"/>
+      <c r="D32" s="182"/>
+      <c r="E32" s="182"/>
+      <c r="F32" s="183"/>
       <c r="G32" s="77"/>
       <c r="H32" s="80">
         <v>4</v>
       </c>
-      <c r="I32" s="190" t="s">
+      <c r="I32" s="172" t="s">
         <v>29</v>
       </c>
-      <c r="J32" s="191"/>
-      <c r="K32" s="191"/>
-      <c r="L32" s="192"/>
+      <c r="J32" s="173"/>
+      <c r="K32" s="173"/>
+      <c r="L32" s="174"/>
     </row>
     <row r="33" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="77"/>
       <c r="B33" s="28">
         <v>5</v>
       </c>
-      <c r="C33" s="193" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" s="194"/>
-      <c r="E33" s="194"/>
-      <c r="F33" s="195"/>
+      <c r="C33" s="233" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="234"/>
+      <c r="E33" s="234"/>
+      <c r="F33" s="235"/>
       <c r="G33" s="77"/>
       <c r="H33" s="80">
         <v>5</v>
       </c>
-      <c r="I33" s="236"/>
-      <c r="J33" s="237"/>
-      <c r="K33" s="237"/>
-      <c r="L33" s="238"/>
+      <c r="I33" s="157"/>
+      <c r="J33" s="158"/>
+      <c r="K33" s="158"/>
+      <c r="L33" s="159"/>
     </row>
     <row r="34" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="78"/>
       <c r="B34" s="90">
         <v>6</v>
       </c>
-      <c r="C34" s="175" t="s">
+      <c r="C34" s="253" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="176"/>
-      <c r="E34" s="176"/>
-      <c r="F34" s="177"/>
+      <c r="D34" s="254"/>
+      <c r="E34" s="254"/>
+      <c r="F34" s="255"/>
       <c r="G34" s="78"/>
       <c r="H34" s="82">
         <v>6</v>
       </c>
-      <c r="I34" s="163" t="s">
+      <c r="I34" s="241" t="s">
         <v>57</v>
       </c>
-      <c r="J34" s="164"/>
-      <c r="K34" s="164"/>
-      <c r="L34" s="165"/>
+      <c r="J34" s="242"/>
+      <c r="K34" s="242"/>
+      <c r="L34" s="243"/>
     </row>
     <row r="35" spans="1:12" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="41"/>
       <c r="B35" s="42"/>
-      <c r="C35" s="171"/>
-      <c r="D35" s="171"/>
-      <c r="E35" s="171"/>
-      <c r="F35" s="171"/>
+      <c r="C35" s="249"/>
+      <c r="D35" s="249"/>
+      <c r="E35" s="249"/>
+      <c r="F35" s="249"/>
       <c r="G35" s="43"/>
       <c r="H35" s="44"/>
-      <c r="I35" s="172"/>
-      <c r="J35" s="173"/>
-      <c r="K35" s="173"/>
-      <c r="L35" s="174"/>
+      <c r="I35" s="250"/>
+      <c r="J35" s="251"/>
+      <c r="K35" s="251"/>
+      <c r="L35" s="252"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A36" s="96"/>
       <c r="B36" s="97" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="170" t="s">
+      <c r="C36" s="248" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="170"/>
-      <c r="E36" s="170"/>
-      <c r="F36" s="170"/>
+      <c r="D36" s="248"/>
+      <c r="E36" s="248"/>
+      <c r="F36" s="248"/>
       <c r="G36" s="96"/>
       <c r="H36" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="166" t="s">
+      <c r="I36" s="244" t="s">
         <v>36</v>
       </c>
-      <c r="J36" s="167"/>
-      <c r="K36" s="167"/>
-      <c r="L36" s="168"/>
+      <c r="J36" s="245"/>
+      <c r="K36" s="245"/>
+      <c r="L36" s="246"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A37" s="98"/>
       <c r="B37" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="169" t="s">
+      <c r="C37" s="247" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="158"/>
-      <c r="E37" s="158"/>
-      <c r="F37" s="159"/>
+      <c r="D37" s="237"/>
+      <c r="E37" s="237"/>
+      <c r="F37" s="238"/>
       <c r="G37" s="98"/>
       <c r="H37" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="I37" s="157" t="s">
+      <c r="I37" s="236" t="s">
         <v>35</v>
       </c>
-      <c r="J37" s="158"/>
-      <c r="K37" s="158"/>
-      <c r="L37" s="159"/>
+      <c r="J37" s="237"/>
+      <c r="K37" s="237"/>
+      <c r="L37" s="238"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A38" s="98"/>
       <c r="B38" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="C38" s="158" t="s">
+      <c r="C38" s="237" t="s">
         <v>58</v>
       </c>
-      <c r="D38" s="158"/>
-      <c r="E38" s="158"/>
-      <c r="F38" s="158"/>
+      <c r="D38" s="237"/>
+      <c r="E38" s="237"/>
+      <c r="F38" s="237"/>
       <c r="G38" s="98"/>
       <c r="H38" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="I38" s="157" t="s">
+      <c r="I38" s="236" t="s">
         <v>58</v>
       </c>
-      <c r="J38" s="158"/>
-      <c r="K38" s="158"/>
-      <c r="L38" s="159"/>
+      <c r="J38" s="237"/>
+      <c r="K38" s="237"/>
+      <c r="L38" s="238"/>
     </row>
     <row r="39" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A39" s="100"/>
       <c r="B39" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="161" t="s">
+      <c r="C39" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="D39" s="161"/>
-      <c r="E39" s="161"/>
-      <c r="F39" s="161"/>
+      <c r="D39" s="226"/>
+      <c r="E39" s="226"/>
+      <c r="F39" s="226"/>
       <c r="G39" s="100"/>
       <c r="H39" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="I39" s="160" t="s">
+      <c r="I39" s="239" t="s">
         <v>56</v>
       </c>
-      <c r="J39" s="161"/>
-      <c r="K39" s="161"/>
-      <c r="L39" s="162"/>
+      <c r="J39" s="226"/>
+      <c r="K39" s="226"/>
+      <c r="L39" s="240"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B40" s="2" t="s">
@@ -4202,29 +4204,47 @@
         <v>55</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>55</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="I19:L19"/>
@@ -4241,36 +4261,18 @@
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C32:F32"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6 K6">
@@ -4324,13 +4326,13 @@
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>11</v>
@@ -4353,11 +4355,11 @@
     <row r="4" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G4" s="1"/>
       <c r="L4" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -4383,7 +4385,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="9" t="s">
@@ -4396,7 +4398,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="9" t="s">
@@ -4466,17 +4468,17 @@
       <c r="A9" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="350" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="350"/>
-      <c r="E9" s="350"/>
-      <c r="F9" s="350"/>
+      <c r="C9" s="268" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="268"/>
+      <c r="E9" s="268"/>
+      <c r="F9" s="268"/>
       <c r="G9" s="11" t="s">
         <v>27</v>
       </c>
       <c r="I9" s="65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J9" s="65"/>
       <c r="K9" s="79"/>
@@ -4515,90 +4517,90 @@
       <c r="B11" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="272" t="s">
+      <c r="C11" s="260" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="273"/>
-      <c r="E11" s="273"/>
-      <c r="F11" s="274"/>
+      <c r="D11" s="261"/>
+      <c r="E11" s="261"/>
+      <c r="F11" s="262"/>
       <c r="G11" s="52" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="272" t="s">
+      <c r="I11" s="260" t="s">
         <v>63</v>
       </c>
-      <c r="J11" s="273"/>
-      <c r="K11" s="273"/>
-      <c r="L11" s="274"/>
-    </row>
-    <row r="12" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J11" s="261"/>
+      <c r="K11" s="261"/>
+      <c r="L11" s="262"/>
+    </row>
+    <row r="12" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="27"/>
       <c r="B12" s="28">
         <v>4</v>
       </c>
-      <c r="C12" s="275" t="s">
-        <v>140</v>
-      </c>
-      <c r="D12" s="276"/>
-      <c r="E12" s="276"/>
-      <c r="F12" s="233"/>
+      <c r="C12" s="342" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="343"/>
+      <c r="E12" s="343"/>
+      <c r="F12" s="211"/>
       <c r="G12" s="27"/>
       <c r="H12" s="28">
         <v>4</v>
       </c>
-      <c r="I12" s="203" t="s">
+      <c r="I12" s="195" t="s">
         <v>44</v>
       </c>
-      <c r="J12" s="204"/>
-      <c r="K12" s="207" t="s">
-        <v>199</v>
-      </c>
-      <c r="L12" s="208"/>
+      <c r="J12" s="196"/>
+      <c r="K12" s="176" t="s">
+        <v>194</v>
+      </c>
+      <c r="L12" s="179"/>
     </row>
     <row r="13" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="27"/>
       <c r="B13" s="28">
         <v>5</v>
       </c>
-      <c r="C13" s="275" t="s">
-        <v>180</v>
-      </c>
-      <c r="D13" s="276"/>
-      <c r="E13" s="276"/>
-      <c r="F13" s="233"/>
+      <c r="C13" s="342" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="343"/>
+      <c r="E13" s="343"/>
+      <c r="F13" s="211"/>
       <c r="G13" s="27"/>
       <c r="H13" s="28">
         <v>5</v>
       </c>
-      <c r="I13" s="203" t="s">
-        <v>141</v>
-      </c>
-      <c r="J13" s="204"/>
-      <c r="K13" s="204" t="s">
+      <c r="I13" s="195" t="s">
+        <v>139</v>
+      </c>
+      <c r="J13" s="196"/>
+      <c r="K13" s="196" t="s">
         <v>45</v>
       </c>
-      <c r="L13" s="205"/>
+      <c r="L13" s="197"/>
     </row>
     <row r="14" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="27"/>
       <c r="B14" s="28">
         <v>6</v>
       </c>
-      <c r="C14" s="277"/>
-      <c r="D14" s="278"/>
-      <c r="E14" s="279"/>
-      <c r="F14" s="280"/>
+      <c r="C14" s="283"/>
+      <c r="D14" s="284"/>
+      <c r="E14" s="285"/>
+      <c r="F14" s="286"/>
       <c r="G14" s="27"/>
       <c r="H14" s="28">
         <v>6</v>
       </c>
-      <c r="I14" s="351"/>
-      <c r="J14" s="352"/>
-      <c r="K14" s="352"/>
-      <c r="L14" s="353"/>
+      <c r="I14" s="256"/>
+      <c r="J14" s="257"/>
+      <c r="K14" s="257"/>
+      <c r="L14" s="258"/>
     </row>
     <row r="15" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
@@ -4607,90 +4609,90 @@
       <c r="B15" s="26">
         <v>1</v>
       </c>
-      <c r="C15" s="281" t="s">
-        <v>137</v>
-      </c>
-      <c r="D15" s="282"/>
-      <c r="E15" s="282"/>
-      <c r="F15" s="283"/>
+      <c r="C15" s="344" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="345"/>
+      <c r="E15" s="345"/>
+      <c r="F15" s="346"/>
       <c r="G15" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H15" s="26">
         <v>1</v>
       </c>
-      <c r="I15" s="281" t="s">
-        <v>137</v>
-      </c>
-      <c r="J15" s="282"/>
-      <c r="K15" s="282"/>
-      <c r="L15" s="283"/>
+      <c r="I15" s="344" t="s">
+        <v>135</v>
+      </c>
+      <c r="J15" s="345"/>
+      <c r="K15" s="345"/>
+      <c r="L15" s="346"/>
     </row>
     <row r="16" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="27"/>
       <c r="B16" s="28">
         <v>2</v>
       </c>
-      <c r="C16" s="190" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" s="191"/>
-      <c r="E16" s="191"/>
-      <c r="F16" s="192"/>
+      <c r="C16" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="173"/>
+      <c r="E16" s="173"/>
+      <c r="F16" s="174"/>
       <c r="G16" s="27"/>
       <c r="H16" s="28">
         <v>2</v>
       </c>
-      <c r="I16" s="357" t="s">
-        <v>136</v>
-      </c>
-      <c r="J16" s="358"/>
-      <c r="K16" s="358"/>
-      <c r="L16" s="359"/>
+      <c r="I16" s="265" t="s">
+        <v>134</v>
+      </c>
+      <c r="J16" s="266"/>
+      <c r="K16" s="266"/>
+      <c r="L16" s="267"/>
     </row>
     <row r="17" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="27"/>
       <c r="B17" s="28">
         <v>3</v>
       </c>
-      <c r="C17" s="236"/>
-      <c r="D17" s="354"/>
-      <c r="E17" s="178" t="s">
-        <v>199</v>
-      </c>
-      <c r="F17" s="179"/>
+      <c r="C17" s="157"/>
+      <c r="D17" s="259"/>
+      <c r="E17" s="225" t="s">
+        <v>194</v>
+      </c>
+      <c r="F17" s="221"/>
       <c r="G17" s="27"/>
       <c r="H17" s="28">
         <v>3</v>
       </c>
-      <c r="I17" s="355" t="s">
+      <c r="I17" s="263" t="s">
         <v>43</v>
       </c>
-      <c r="J17" s="356"/>
-      <c r="K17" s="207" t="s">
-        <v>142</v>
-      </c>
-      <c r="L17" s="208"/>
+      <c r="J17" s="264"/>
+      <c r="K17" s="176" t="s">
+        <v>140</v>
+      </c>
+      <c r="L17" s="179"/>
     </row>
     <row r="18" spans="1:12" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="27"/>
       <c r="B18" s="28">
         <v>4</v>
       </c>
-      <c r="C18" s="289"/>
-      <c r="D18" s="290"/>
-      <c r="E18" s="290"/>
-      <c r="F18" s="285"/>
+      <c r="C18" s="352"/>
+      <c r="D18" s="353"/>
+      <c r="E18" s="353"/>
+      <c r="F18" s="348"/>
       <c r="G18" s="27"/>
       <c r="H18" s="28">
         <v>4</v>
       </c>
-      <c r="I18" s="323" t="s">
-        <v>138</v>
-      </c>
-      <c r="J18" s="324"/>
-      <c r="K18" s="284"/>
-      <c r="L18" s="285"/>
+      <c r="I18" s="281" t="s">
+        <v>136</v>
+      </c>
+      <c r="J18" s="282"/>
+      <c r="K18" s="347"/>
+      <c r="L18" s="348"/>
     </row>
     <row r="19" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="22" t="s">
@@ -4699,90 +4701,90 @@
       <c r="B19" s="26">
         <v>1</v>
       </c>
-      <c r="C19" s="186" t="s">
-        <v>143</v>
-      </c>
-      <c r="D19" s="187"/>
-      <c r="E19" s="188"/>
-      <c r="F19" s="189"/>
+      <c r="C19" s="229" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="230"/>
+      <c r="E19" s="231"/>
+      <c r="F19" s="232"/>
       <c r="G19" s="22" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="26">
         <v>1</v>
       </c>
-      <c r="I19" s="286"/>
-      <c r="J19" s="188"/>
-      <c r="K19" s="287" t="s">
-        <v>199</v>
-      </c>
-      <c r="L19" s="288"/>
+      <c r="I19" s="349"/>
+      <c r="J19" s="231"/>
+      <c r="K19" s="350" t="s">
+        <v>194</v>
+      </c>
+      <c r="L19" s="351"/>
     </row>
     <row r="20" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="27"/>
       <c r="B20" s="28">
         <v>2</v>
       </c>
-      <c r="C20" s="203" t="s">
+      <c r="C20" s="195" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="204"/>
-      <c r="E20" s="204"/>
-      <c r="F20" s="205"/>
+      <c r="D20" s="196"/>
+      <c r="E20" s="196"/>
+      <c r="F20" s="197"/>
       <c r="G20" s="27"/>
       <c r="H20" s="28">
         <v>2</v>
       </c>
-      <c r="I20" s="203"/>
-      <c r="J20" s="204"/>
-      <c r="K20" s="207" t="s">
-        <v>71</v>
-      </c>
-      <c r="L20" s="208"/>
+      <c r="I20" s="195"/>
+      <c r="J20" s="196"/>
+      <c r="K20" s="176" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20" s="179"/>
     </row>
     <row r="21" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="27"/>
       <c r="B21" s="28">
         <v>3</v>
       </c>
-      <c r="C21" s="201" t="s">
-        <v>187</v>
-      </c>
-      <c r="D21" s="202"/>
-      <c r="E21" s="202"/>
-      <c r="F21" s="245"/>
+      <c r="C21" s="166" t="s">
+        <v>183</v>
+      </c>
+      <c r="D21" s="167"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="168"/>
       <c r="G21" s="27"/>
       <c r="H21" s="28">
         <v>3</v>
       </c>
-      <c r="I21" s="203" t="s">
-        <v>144</v>
-      </c>
-      <c r="J21" s="204"/>
-      <c r="K21" s="204"/>
-      <c r="L21" s="205"/>
+      <c r="I21" s="195" t="s">
+        <v>142</v>
+      </c>
+      <c r="J21" s="196"/>
+      <c r="K21" s="196"/>
+      <c r="L21" s="197"/>
     </row>
     <row r="22" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="27"/>
       <c r="B22" s="28">
         <v>4</v>
       </c>
-      <c r="C22" s="340"/>
-      <c r="D22" s="341"/>
-      <c r="E22" s="256" t="s">
-        <v>148</v>
-      </c>
-      <c r="F22" s="257"/>
+      <c r="C22" s="269"/>
+      <c r="D22" s="305"/>
+      <c r="E22" s="354" t="s">
+        <v>146</v>
+      </c>
+      <c r="F22" s="355"/>
       <c r="G22" s="27"/>
       <c r="H22" s="28">
         <v>4</v>
       </c>
-      <c r="I22" s="258" t="s">
+      <c r="I22" s="356" t="s">
         <v>43</v>
       </c>
-      <c r="J22" s="259"/>
-      <c r="K22" s="260"/>
-      <c r="L22" s="261"/>
+      <c r="J22" s="357"/>
+      <c r="K22" s="358"/>
+      <c r="L22" s="359"/>
     </row>
     <row r="23" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="22" t="s">
@@ -4791,90 +4793,90 @@
       <c r="B23" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="325" t="s">
+      <c r="C23" s="290" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="326"/>
-      <c r="E23" s="326"/>
-      <c r="F23" s="327"/>
+      <c r="D23" s="291"/>
+      <c r="E23" s="291"/>
+      <c r="F23" s="292"/>
       <c r="G23" s="22" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="I23" s="325" t="s">
+      <c r="I23" s="290" t="s">
         <v>63</v>
       </c>
-      <c r="J23" s="326"/>
-      <c r="K23" s="326"/>
-      <c r="L23" s="327"/>
+      <c r="J23" s="291"/>
+      <c r="K23" s="291"/>
+      <c r="L23" s="292"/>
     </row>
     <row r="24" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="27"/>
       <c r="B24" s="28">
         <v>4</v>
       </c>
-      <c r="C24" s="333" t="s">
+      <c r="C24" s="298" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="334"/>
-      <c r="E24" s="334"/>
-      <c r="F24" s="335"/>
+      <c r="D24" s="299"/>
+      <c r="E24" s="299"/>
+      <c r="F24" s="300"/>
       <c r="G24" s="27"/>
       <c r="H24" s="28">
         <v>4</v>
       </c>
-      <c r="I24" s="336" t="s">
-        <v>196</v>
-      </c>
-      <c r="J24" s="337"/>
-      <c r="K24" s="338" t="s">
-        <v>145</v>
-      </c>
-      <c r="L24" s="339"/>
+      <c r="I24" s="301" t="s">
+        <v>191</v>
+      </c>
+      <c r="J24" s="302"/>
+      <c r="K24" s="303" t="s">
+        <v>143</v>
+      </c>
+      <c r="L24" s="304"/>
     </row>
     <row r="25" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="84"/>
       <c r="B25" s="28">
         <v>5</v>
       </c>
-      <c r="C25" s="190" t="s">
-        <v>143</v>
-      </c>
-      <c r="D25" s="328"/>
-      <c r="E25" s="329" t="s">
-        <v>190</v>
-      </c>
-      <c r="F25" s="192"/>
+      <c r="C25" s="172" t="s">
+        <v>141</v>
+      </c>
+      <c r="D25" s="293"/>
+      <c r="E25" s="294" t="s">
+        <v>185</v>
+      </c>
+      <c r="F25" s="174"/>
       <c r="G25" s="84"/>
       <c r="H25" s="56">
         <v>5</v>
       </c>
-      <c r="I25" s="292" t="s">
-        <v>139</v>
-      </c>
-      <c r="J25" s="293"/>
-      <c r="K25" s="293"/>
-      <c r="L25" s="294"/>
+      <c r="I25" s="307" t="s">
+        <v>137</v>
+      </c>
+      <c r="J25" s="308"/>
+      <c r="K25" s="308"/>
+      <c r="L25" s="309"/>
     </row>
     <row r="26" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="29"/>
       <c r="B26" s="28">
         <v>6</v>
       </c>
-      <c r="C26" s="277"/>
-      <c r="D26" s="278"/>
-      <c r="E26" s="279"/>
-      <c r="F26" s="280"/>
+      <c r="C26" s="283"/>
+      <c r="D26" s="284"/>
+      <c r="E26" s="285"/>
+      <c r="F26" s="286"/>
       <c r="G26" s="29"/>
       <c r="H26" s="28">
         <v>6</v>
       </c>
-      <c r="I26" s="314"/>
-      <c r="J26" s="315"/>
-      <c r="K26" s="315"/>
-      <c r="L26" s="316"/>
+      <c r="I26" s="323"/>
+      <c r="J26" s="324"/>
+      <c r="K26" s="324"/>
+      <c r="L26" s="325"/>
     </row>
     <row r="27" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
@@ -4883,90 +4885,90 @@
       <c r="B27" s="26">
         <v>1</v>
       </c>
-      <c r="C27" s="317"/>
-      <c r="D27" s="318"/>
-      <c r="E27" s="318"/>
-      <c r="F27" s="319"/>
+      <c r="C27" s="326"/>
+      <c r="D27" s="327"/>
+      <c r="E27" s="327"/>
+      <c r="F27" s="328"/>
       <c r="G27" s="22" t="s">
         <v>25</v>
       </c>
       <c r="H27" s="26">
         <v>1</v>
       </c>
-      <c r="I27" s="320" t="s">
-        <v>72</v>
-      </c>
-      <c r="J27" s="321"/>
-      <c r="K27" s="321"/>
-      <c r="L27" s="322"/>
+      <c r="I27" s="329" t="s">
+        <v>71</v>
+      </c>
+      <c r="J27" s="330"/>
+      <c r="K27" s="330"/>
+      <c r="L27" s="331"/>
     </row>
     <row r="28" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="53"/>
       <c r="B28" s="28">
         <v>2</v>
       </c>
-      <c r="C28" s="301" t="s">
-        <v>147</v>
-      </c>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
-      <c r="F28" s="303"/>
+      <c r="C28" s="287" t="s">
+        <v>145</v>
+      </c>
+      <c r="D28" s="288"/>
+      <c r="E28" s="288"/>
+      <c r="F28" s="289"/>
       <c r="G28" s="53"/>
       <c r="H28" s="28">
         <v>2</v>
       </c>
-      <c r="I28" s="330" t="s">
-        <v>146</v>
-      </c>
-      <c r="J28" s="331"/>
-      <c r="K28" s="331"/>
-      <c r="L28" s="332"/>
+      <c r="I28" s="295" t="s">
+        <v>144</v>
+      </c>
+      <c r="J28" s="296"/>
+      <c r="K28" s="296"/>
+      <c r="L28" s="297"/>
     </row>
     <row r="29" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="53"/>
       <c r="B29" s="28">
         <v>3</v>
       </c>
-      <c r="C29" s="301" t="s">
+      <c r="C29" s="287" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="302"/>
-      <c r="E29" s="302" t="s">
-        <v>206</v>
-      </c>
-      <c r="F29" s="303"/>
+      <c r="D29" s="288"/>
+      <c r="E29" s="288" t="s">
+        <v>201</v>
+      </c>
+      <c r="F29" s="289"/>
       <c r="G29" s="53"/>
       <c r="H29" s="28">
         <v>3</v>
       </c>
-      <c r="I29" s="298" t="s">
-        <v>140</v>
-      </c>
-      <c r="J29" s="299"/>
-      <c r="K29" s="299"/>
-      <c r="L29" s="300"/>
+      <c r="I29" s="310" t="s">
+        <v>138</v>
+      </c>
+      <c r="J29" s="311"/>
+      <c r="K29" s="311"/>
+      <c r="L29" s="312"/>
     </row>
     <row r="30" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="57"/>
       <c r="B30" s="30">
         <v>4</v>
       </c>
-      <c r="C30" s="268" t="s">
-        <v>149</v>
-      </c>
-      <c r="D30" s="269"/>
-      <c r="E30" s="270" t="s">
-        <v>70</v>
-      </c>
-      <c r="F30" s="271"/>
+      <c r="C30" s="338" t="s">
+        <v>206</v>
+      </c>
+      <c r="D30" s="339"/>
+      <c r="E30" s="340" t="s">
+        <v>207</v>
+      </c>
+      <c r="F30" s="341"/>
       <c r="G30" s="57"/>
       <c r="H30" s="30">
         <v>4</v>
       </c>
-      <c r="I30" s="262"/>
-      <c r="J30" s="263"/>
-      <c r="K30" s="263"/>
-      <c r="L30" s="264"/>
+      <c r="I30" s="332"/>
+      <c r="J30" s="333"/>
+      <c r="K30" s="333"/>
+      <c r="L30" s="334"/>
     </row>
     <row r="31" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="104" t="s">
@@ -4975,68 +4977,68 @@
       <c r="B31" s="25">
         <v>2</v>
       </c>
-      <c r="C31" s="295" t="s">
-        <v>150</v>
-      </c>
-      <c r="D31" s="296"/>
-      <c r="E31" s="296"/>
-      <c r="F31" s="297"/>
+      <c r="C31" s="278" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" s="279"/>
+      <c r="E31" s="279"/>
+      <c r="F31" s="280"/>
       <c r="G31" s="58" t="s">
         <v>26</v>
       </c>
       <c r="H31" s="26">
         <v>1</v>
       </c>
-      <c r="I31" s="295" t="s">
-        <v>150</v>
-      </c>
-      <c r="J31" s="296"/>
-      <c r="K31" s="296"/>
-      <c r="L31" s="297"/>
+      <c r="I31" s="278" t="s">
+        <v>147</v>
+      </c>
+      <c r="J31" s="279"/>
+      <c r="K31" s="279"/>
+      <c r="L31" s="280"/>
     </row>
     <row r="32" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="53"/>
       <c r="B32" s="28">
         <v>3</v>
       </c>
-      <c r="C32" s="307"/>
-      <c r="D32" s="308"/>
-      <c r="E32" s="309"/>
-      <c r="F32" s="310"/>
+      <c r="C32" s="316"/>
+      <c r="D32" s="317"/>
+      <c r="E32" s="318"/>
+      <c r="F32" s="319"/>
       <c r="G32" s="54"/>
       <c r="H32" s="28">
         <v>2</v>
       </c>
-      <c r="I32" s="307"/>
-      <c r="J32" s="309"/>
-      <c r="K32" s="309"/>
-      <c r="L32" s="310"/>
+      <c r="I32" s="316"/>
+      <c r="J32" s="318"/>
+      <c r="K32" s="318"/>
+      <c r="L32" s="319"/>
     </row>
     <row r="33" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="57"/>
       <c r="B33" s="30">
         <v>4</v>
       </c>
-      <c r="C33" s="311"/>
-      <c r="D33" s="312"/>
-      <c r="E33" s="312"/>
-      <c r="F33" s="313"/>
+      <c r="C33" s="320"/>
+      <c r="D33" s="321"/>
+      <c r="E33" s="321"/>
+      <c r="F33" s="322"/>
       <c r="G33" s="59"/>
       <c r="H33" s="30">
         <v>3</v>
       </c>
-      <c r="I33" s="340"/>
-      <c r="J33" s="342"/>
-      <c r="K33" s="342"/>
-      <c r="L33" s="343"/>
+      <c r="I33" s="269"/>
+      <c r="J33" s="270"/>
+      <c r="K33" s="270"/>
+      <c r="L33" s="271"/>
     </row>
     <row r="34" spans="1:12" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="60"/>
       <c r="B34" s="61"/>
-      <c r="C34" s="344"/>
-      <c r="D34" s="345"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="272"/>
+      <c r="D34" s="273"/>
+      <c r="E34" s="273"/>
+      <c r="F34" s="274"/>
       <c r="G34" s="62"/>
       <c r="H34" s="61"/>
       <c r="I34" s="87"/>
@@ -5049,88 +5051,88 @@
       <c r="B35" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="347" t="s">
-        <v>117</v>
-      </c>
-      <c r="D35" s="348"/>
-      <c r="E35" s="348"/>
-      <c r="F35" s="349"/>
+      <c r="C35" s="275" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" s="276"/>
+      <c r="E35" s="276"/>
+      <c r="F35" s="277"/>
       <c r="G35" s="63"/>
       <c r="H35" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="I35" s="347" t="s">
-        <v>117</v>
-      </c>
-      <c r="J35" s="348"/>
-      <c r="K35" s="348"/>
-      <c r="L35" s="349"/>
+      <c r="I35" s="275" t="s">
+        <v>116</v>
+      </c>
+      <c r="J35" s="276"/>
+      <c r="K35" s="276"/>
+      <c r="L35" s="277"/>
     </row>
     <row r="36" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="53"/>
       <c r="B36" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="265" t="s">
+      <c r="C36" s="335" t="s">
         <v>42</v>
       </c>
-      <c r="D36" s="266"/>
-      <c r="E36" s="266"/>
-      <c r="F36" s="267"/>
+      <c r="D36" s="336"/>
+      <c r="E36" s="336"/>
+      <c r="F36" s="337"/>
       <c r="G36" s="53"/>
       <c r="H36" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="201" t="s">
+      <c r="I36" s="166" t="s">
         <v>42</v>
       </c>
-      <c r="J36" s="202"/>
-      <c r="K36" s="202"/>
-      <c r="L36" s="245"/>
+      <c r="J36" s="167"/>
+      <c r="K36" s="167"/>
+      <c r="L36" s="168"/>
     </row>
     <row r="37" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="64"/>
       <c r="B37" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="304" t="s">
+      <c r="C37" s="313" t="s">
         <v>41</v>
       </c>
-      <c r="D37" s="305"/>
-      <c r="E37" s="305"/>
-      <c r="F37" s="306"/>
+      <c r="D37" s="314"/>
+      <c r="E37" s="314"/>
+      <c r="F37" s="315"/>
       <c r="G37" s="64"/>
       <c r="H37" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="I37" s="304" t="s">
+      <c r="I37" s="313" t="s">
         <v>41</v>
       </c>
-      <c r="J37" s="305"/>
-      <c r="K37" s="305"/>
-      <c r="L37" s="306"/>
+      <c r="J37" s="314"/>
+      <c r="K37" s="314"/>
+      <c r="L37" s="315"/>
     </row>
     <row r="38" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="85" t="s">
         <v>64</v>
       </c>
       <c r="B38" s="86"/>
-      <c r="C38" s="291" t="s">
-        <v>151</v>
-      </c>
-      <c r="D38" s="291"/>
-      <c r="E38" s="291"/>
-      <c r="F38" s="291"/>
+      <c r="C38" s="306" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" s="306"/>
+      <c r="E38" s="306"/>
+      <c r="F38" s="306"/>
       <c r="G38" s="85" t="s">
         <v>64</v>
       </c>
       <c r="H38" s="86"/>
-      <c r="I38" s="291" t="s">
-        <v>151</v>
-      </c>
-      <c r="J38" s="291"/>
-      <c r="K38" s="291"/>
-      <c r="L38" s="291"/>
+      <c r="I38" s="306" t="s">
+        <v>148</v>
+      </c>
+      <c r="J38" s="306"/>
+      <c r="K38" s="306"/>
+      <c r="L38" s="306"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
@@ -5151,35 +5153,54 @@
         <v>55</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>55</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="I27:L27"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C28:F28"/>
@@ -5196,43 +5217,24 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="I16:L16"/>
   </mergeCells>
   <conditionalFormatting sqref="C9:D9">
     <cfRule type="expression" priority="3">
@@ -5310,7 +5312,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="115" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" s="106"/>
       <c r="C2" s="106"/>
@@ -5320,7 +5322,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="115" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H2" s="106"/>
       <c r="I2" s="106"/>
@@ -5355,11 +5357,11 @@
     <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="114" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G4" s="1"/>
       <c r="L4" s="114" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -5386,7 +5388,7 @@
       </c>
       <c r="B6" s="106"/>
       <c r="C6" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" s="107"/>
       <c r="E6" s="108" t="s">
@@ -5400,7 +5402,7 @@
       </c>
       <c r="H6" s="106"/>
       <c r="I6" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J6" s="107"/>
       <c r="K6" s="108" t="s">
@@ -5475,12 +5477,12 @@
         <v>27</v>
       </c>
       <c r="B9" s="106"/>
-      <c r="C9" s="428" t="s">
+      <c r="C9" s="392" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="428"/>
-      <c r="E9" s="428"/>
-      <c r="F9" s="428"/>
+      <c r="D9" s="392"/>
+      <c r="E9" s="392"/>
+      <c r="F9" s="392"/>
       <c r="G9" s="110" t="s">
         <v>27</v>
       </c>
@@ -5497,20 +5499,20 @@
         <v>34</v>
       </c>
       <c r="B10" s="106"/>
-      <c r="C10" s="214" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" s="214"/>
+      <c r="C10" s="185" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="185"/>
       <c r="E10" s="113"/>
       <c r="F10" s="113"/>
       <c r="G10" s="110" t="s">
         <v>34</v>
       </c>
       <c r="H10" s="106"/>
-      <c r="I10" s="214" t="s">
-        <v>104</v>
-      </c>
-      <c r="J10" s="214"/>
+      <c r="I10" s="185" t="s">
+        <v>103</v>
+      </c>
+      <c r="J10" s="185"/>
       <c r="K10" s="103"/>
       <c r="L10" s="106"/>
     </row>
@@ -5547,114 +5549,112 @@
       <c r="B12" s="26">
         <v>1</v>
       </c>
-      <c r="C12" s="363"/>
-      <c r="D12" s="364"/>
-      <c r="E12" s="364"/>
-      <c r="F12" s="429"/>
+      <c r="C12" s="370"/>
+      <c r="D12" s="371"/>
+      <c r="E12" s="371"/>
+      <c r="F12" s="372"/>
       <c r="G12" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="26">
         <v>1</v>
       </c>
-      <c r="I12" s="442" t="s">
-        <v>188</v>
-      </c>
-      <c r="J12" s="443"/>
-      <c r="K12" s="443"/>
-      <c r="L12" s="444"/>
+      <c r="I12" s="364"/>
+      <c r="J12" s="365"/>
+      <c r="K12" s="365"/>
+      <c r="L12" s="366"/>
     </row>
     <row r="13" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="27"/>
       <c r="B13" s="28">
         <v>2</v>
       </c>
-      <c r="C13" s="394" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="395"/>
-      <c r="E13" s="395"/>
-      <c r="F13" s="396"/>
+      <c r="C13" s="374" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="375"/>
+      <c r="E13" s="375"/>
+      <c r="F13" s="376"/>
       <c r="G13" s="27"/>
       <c r="H13" s="28">
         <v>2</v>
       </c>
-      <c r="I13" s="394" t="s">
-        <v>189</v>
-      </c>
-      <c r="J13" s="395"/>
-      <c r="K13" s="395"/>
-      <c r="L13" s="396"/>
+      <c r="I13" s="374" t="s">
+        <v>184</v>
+      </c>
+      <c r="J13" s="375"/>
+      <c r="K13" s="375"/>
+      <c r="L13" s="376"/>
     </row>
     <row r="14" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="27"/>
       <c r="B14" s="28">
         <v>3</v>
       </c>
-      <c r="C14" s="394" t="s">
-        <v>157</v>
-      </c>
-      <c r="D14" s="395"/>
-      <c r="E14" s="395"/>
-      <c r="F14" s="396"/>
+      <c r="C14" s="374" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14" s="375"/>
+      <c r="E14" s="375"/>
+      <c r="F14" s="376"/>
       <c r="G14" s="27"/>
       <c r="H14" s="28">
         <v>3</v>
       </c>
-      <c r="I14" s="394" t="s">
-        <v>75</v>
-      </c>
-      <c r="J14" s="395"/>
-      <c r="K14" s="395"/>
-      <c r="L14" s="396"/>
+      <c r="I14" s="374" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" s="375"/>
+      <c r="K14" s="375"/>
+      <c r="L14" s="376"/>
     </row>
     <row r="15" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="84"/>
       <c r="B15" s="56">
         <v>4</v>
       </c>
-      <c r="C15" s="394" t="s">
-        <v>158</v>
-      </c>
-      <c r="D15" s="395"/>
-      <c r="E15" s="395" t="s">
-        <v>185</v>
-      </c>
-      <c r="F15" s="396"/>
+      <c r="C15" s="374" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" s="375"/>
+      <c r="E15" s="375" t="s">
+        <v>181</v>
+      </c>
+      <c r="F15" s="376"/>
       <c r="G15" s="84"/>
       <c r="H15" s="56">
         <v>4</v>
       </c>
-      <c r="I15" s="394" t="s">
+      <c r="I15" s="374" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="395"/>
-      <c r="K15" s="395" t="s">
-        <v>159</v>
-      </c>
-      <c r="L15" s="396"/>
+      <c r="J15" s="375"/>
+      <c r="K15" s="375" t="s">
+        <v>156</v>
+      </c>
+      <c r="L15" s="376"/>
     </row>
     <row r="16" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="29"/>
       <c r="B16" s="30">
         <v>5</v>
       </c>
-      <c r="C16" s="438"/>
-      <c r="D16" s="439"/>
-      <c r="E16" s="439"/>
-      <c r="F16" s="440"/>
+      <c r="C16" s="386"/>
+      <c r="D16" s="387"/>
+      <c r="E16" s="387"/>
+      <c r="F16" s="388"/>
       <c r="G16" s="29"/>
       <c r="H16" s="30">
         <v>5</v>
       </c>
-      <c r="I16" s="435" t="s">
-        <v>200</v>
-      </c>
-      <c r="J16" s="436"/>
-      <c r="K16" s="436" t="s">
-        <v>79</v>
-      </c>
-      <c r="L16" s="437"/>
+      <c r="I16" s="397" t="s">
+        <v>195</v>
+      </c>
+      <c r="J16" s="384"/>
+      <c r="K16" s="384" t="s">
+        <v>78</v>
+      </c>
+      <c r="L16" s="385"/>
     </row>
     <row r="17" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="52" t="s">
@@ -5663,92 +5663,90 @@
       <c r="B17" s="25">
         <v>2</v>
       </c>
-      <c r="C17" s="430" t="s">
+      <c r="C17" s="393" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" s="362"/>
+      <c r="E17" s="362" t="s">
         <v>161</v>
       </c>
-      <c r="D17" s="431"/>
-      <c r="E17" s="431" t="s">
-        <v>164</v>
-      </c>
-      <c r="F17" s="441"/>
+      <c r="F17" s="363"/>
       <c r="G17" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H17" s="26">
         <v>1</v>
       </c>
-      <c r="I17" s="432"/>
-      <c r="J17" s="433"/>
-      <c r="K17" s="433"/>
-      <c r="L17" s="434"/>
+      <c r="I17" s="394"/>
+      <c r="J17" s="395"/>
+      <c r="K17" s="395"/>
+      <c r="L17" s="396"/>
     </row>
     <row r="18" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="27"/>
       <c r="B18" s="25">
         <v>3</v>
       </c>
-      <c r="C18" s="365"/>
-      <c r="D18" s="366"/>
-      <c r="E18" s="380" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="381"/>
+      <c r="C18" s="437"/>
+      <c r="D18" s="438"/>
+      <c r="E18" s="382" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="383"/>
       <c r="G18" s="27"/>
       <c r="H18" s="25">
         <v>2</v>
       </c>
-      <c r="I18" s="374"/>
-      <c r="J18" s="375"/>
-      <c r="K18" s="376" t="s">
-        <v>91</v>
-      </c>
-      <c r="L18" s="377"/>
+      <c r="I18" s="446"/>
+      <c r="J18" s="447"/>
+      <c r="K18" s="360" t="s">
+        <v>90</v>
+      </c>
+      <c r="L18" s="361"/>
     </row>
     <row r="19" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="27"/>
       <c r="B19" s="28">
         <v>4</v>
       </c>
-      <c r="C19" s="365"/>
-      <c r="D19" s="367"/>
-      <c r="E19" s="367"/>
-      <c r="F19" s="368"/>
+      <c r="C19" s="437"/>
+      <c r="D19" s="439"/>
+      <c r="E19" s="439"/>
+      <c r="F19" s="440"/>
       <c r="G19" s="27"/>
       <c r="H19" s="28">
         <v>3</v>
       </c>
-      <c r="I19" s="372" t="s">
-        <v>92</v>
-      </c>
-      <c r="J19" s="373"/>
-      <c r="K19" s="376" t="s">
-        <v>160</v>
-      </c>
-      <c r="L19" s="377"/>
+      <c r="I19" s="444" t="s">
+        <v>91</v>
+      </c>
+      <c r="J19" s="445"/>
+      <c r="K19" s="360" t="s">
+        <v>157</v>
+      </c>
+      <c r="L19" s="361"/>
     </row>
     <row r="20" spans="1:12" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="27"/>
       <c r="B20" s="28">
         <v>5</v>
       </c>
-      <c r="C20" s="369" t="s">
-        <v>188</v>
-      </c>
-      <c r="D20" s="370"/>
-      <c r="E20" s="370"/>
-      <c r="F20" s="371"/>
+      <c r="C20" s="441"/>
+      <c r="D20" s="442"/>
+      <c r="E20" s="442"/>
+      <c r="F20" s="443"/>
       <c r="G20" s="27"/>
       <c r="H20" s="28">
         <v>4</v>
       </c>
-      <c r="I20" s="378" t="s">
-        <v>162</v>
-      </c>
-      <c r="J20" s="379"/>
-      <c r="K20" s="380" t="s">
-        <v>163</v>
-      </c>
-      <c r="L20" s="381"/>
+      <c r="I20" s="430" t="s">
+        <v>159</v>
+      </c>
+      <c r="J20" s="431"/>
+      <c r="K20" s="382" t="s">
+        <v>160</v>
+      </c>
+      <c r="L20" s="383"/>
     </row>
     <row r="21" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="22" t="s">
@@ -5757,94 +5755,94 @@
       <c r="B21" s="26">
         <v>2</v>
       </c>
-      <c r="C21" s="360" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21" s="361"/>
-      <c r="E21" s="361"/>
-      <c r="F21" s="362"/>
+      <c r="C21" s="434" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="435"/>
+      <c r="E21" s="435"/>
+      <c r="F21" s="436"/>
       <c r="G21" s="22" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="26">
         <v>2</v>
       </c>
-      <c r="I21" s="363" t="s">
-        <v>203</v>
-      </c>
-      <c r="J21" s="364"/>
-      <c r="K21" s="382"/>
-      <c r="L21" s="383"/>
+      <c r="I21" s="370" t="s">
+        <v>198</v>
+      </c>
+      <c r="J21" s="371"/>
+      <c r="K21" s="432"/>
+      <c r="L21" s="433"/>
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="27"/>
       <c r="B22" s="28">
         <v>3</v>
       </c>
-      <c r="C22" s="394" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="395"/>
-      <c r="E22" s="395"/>
-      <c r="F22" s="396"/>
+      <c r="C22" s="374" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" s="375"/>
+      <c r="E22" s="375"/>
+      <c r="F22" s="376"/>
       <c r="G22" s="27"/>
       <c r="H22" s="28">
         <v>3</v>
       </c>
-      <c r="I22" s="394" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="395"/>
-      <c r="K22" s="395"/>
-      <c r="L22" s="396"/>
+      <c r="I22" s="374" t="s">
+        <v>149</v>
+      </c>
+      <c r="J22" s="375"/>
+      <c r="K22" s="375"/>
+      <c r="L22" s="376"/>
     </row>
     <row r="23" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="27"/>
       <c r="B23" s="28">
         <v>4</v>
       </c>
-      <c r="C23" s="394" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="395"/>
-      <c r="E23" s="395" t="s">
-        <v>165</v>
-      </c>
-      <c r="F23" s="396"/>
+      <c r="C23" s="374" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="375"/>
+      <c r="E23" s="375" t="s">
+        <v>162</v>
+      </c>
+      <c r="F23" s="376"/>
       <c r="G23" s="27"/>
       <c r="H23" s="28">
         <v>4</v>
       </c>
-      <c r="I23" s="386" t="s">
-        <v>78</v>
-      </c>
-      <c r="J23" s="376"/>
-      <c r="K23" s="376"/>
-      <c r="L23" s="377"/>
+      <c r="I23" s="373" t="s">
+        <v>77</v>
+      </c>
+      <c r="J23" s="360"/>
+      <c r="K23" s="360"/>
+      <c r="L23" s="361"/>
     </row>
     <row r="24" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="29"/>
       <c r="B24" s="30">
         <v>5</v>
       </c>
-      <c r="C24" s="384" t="s">
-        <v>166</v>
-      </c>
-      <c r="D24" s="385"/>
-      <c r="E24" s="448"/>
-      <c r="F24" s="449"/>
+      <c r="C24" s="381" t="s">
+        <v>163</v>
+      </c>
+      <c r="D24" s="379"/>
+      <c r="E24" s="377"/>
+      <c r="F24" s="378"/>
       <c r="G24" s="29"/>
       <c r="H24" s="30">
         <v>5</v>
       </c>
-      <c r="I24" s="384" t="s">
-        <v>73</v>
-      </c>
-      <c r="J24" s="385"/>
-      <c r="K24" s="385" t="s">
-        <v>80</v>
-      </c>
-      <c r="L24" s="450"/>
+      <c r="I24" s="381" t="s">
+        <v>72</v>
+      </c>
+      <c r="J24" s="379"/>
+      <c r="K24" s="379" t="s">
+        <v>79</v>
+      </c>
+      <c r="L24" s="380"/>
     </row>
     <row r="25" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="22" t="s">
@@ -5853,84 +5851,86 @@
       <c r="B25" s="26">
         <v>2</v>
       </c>
-      <c r="C25" s="409"/>
-      <c r="D25" s="410"/>
-      <c r="E25" s="410"/>
-      <c r="F25" s="411"/>
+      <c r="C25" s="427" t="s">
+        <v>205</v>
+      </c>
+      <c r="D25" s="428"/>
+      <c r="E25" s="428"/>
+      <c r="F25" s="429"/>
       <c r="G25" s="52" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="25">
         <v>2</v>
       </c>
-      <c r="I25" s="390"/>
-      <c r="J25" s="391"/>
-      <c r="K25" s="392"/>
-      <c r="L25" s="393"/>
+      <c r="I25" s="419"/>
+      <c r="J25" s="420"/>
+      <c r="K25" s="421"/>
+      <c r="L25" s="422"/>
     </row>
     <row r="26" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="27"/>
       <c r="B26" s="28">
         <v>3</v>
       </c>
-      <c r="C26" s="386" t="s">
-        <v>153</v>
-      </c>
-      <c r="D26" s="376"/>
-      <c r="E26" s="376"/>
-      <c r="F26" s="377"/>
+      <c r="C26" s="373" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="360"/>
+      <c r="E26" s="360"/>
+      <c r="F26" s="361"/>
       <c r="G26" s="27"/>
       <c r="H26" s="28">
         <v>3</v>
       </c>
-      <c r="I26" s="397"/>
-      <c r="J26" s="398"/>
-      <c r="K26" s="376" t="s">
+      <c r="I26" s="423"/>
+      <c r="J26" s="424"/>
+      <c r="K26" s="360" t="s">
         <v>51</v>
       </c>
-      <c r="L26" s="377"/>
+      <c r="L26" s="361"/>
     </row>
     <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="27"/>
       <c r="B27" s="28">
         <v>4</v>
       </c>
-      <c r="C27" s="406" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" s="407"/>
-      <c r="E27" s="407"/>
-      <c r="F27" s="408"/>
+      <c r="C27" s="413" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="414"/>
+      <c r="E27" s="414"/>
+      <c r="F27" s="415"/>
       <c r="G27" s="27"/>
       <c r="H27" s="28">
         <v>4</v>
       </c>
-      <c r="I27" s="394" t="s">
-        <v>154</v>
-      </c>
-      <c r="J27" s="395"/>
-      <c r="K27" s="395"/>
-      <c r="L27" s="396"/>
+      <c r="I27" s="374" t="s">
+        <v>151</v>
+      </c>
+      <c r="J27" s="375"/>
+      <c r="K27" s="375"/>
+      <c r="L27" s="376"/>
     </row>
     <row r="28" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="29"/>
       <c r="B28" s="30">
         <v>5</v>
       </c>
-      <c r="C28" s="403"/>
-      <c r="D28" s="404"/>
-      <c r="E28" s="404"/>
-      <c r="F28" s="405"/>
+      <c r="C28" s="407"/>
+      <c r="D28" s="408"/>
+      <c r="E28" s="408"/>
+      <c r="F28" s="409"/>
       <c r="G28" s="29"/>
       <c r="H28" s="30">
         <v>5</v>
       </c>
-      <c r="I28" s="399" t="s">
-        <v>92</v>
-      </c>
-      <c r="J28" s="400"/>
-      <c r="K28" s="401"/>
-      <c r="L28" s="402"/>
+      <c r="I28" s="398" t="s">
+        <v>91</v>
+      </c>
+      <c r="J28" s="425"/>
+      <c r="K28" s="426"/>
+      <c r="L28" s="406"/>
     </row>
     <row r="29" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="22" t="s">
@@ -5939,88 +5939,90 @@
       <c r="B29" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="445" t="s">
+      <c r="C29" s="367" t="s">
         <v>65</v>
       </c>
-      <c r="D29" s="446"/>
-      <c r="E29" s="446"/>
-      <c r="F29" s="447"/>
+      <c r="D29" s="368"/>
+      <c r="E29" s="368"/>
+      <c r="F29" s="369"/>
       <c r="G29" s="22" t="s">
         <v>25</v>
       </c>
       <c r="H29" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="I29" s="363" t="s">
+      <c r="I29" s="370" t="s">
         <v>65</v>
       </c>
-      <c r="J29" s="364"/>
-      <c r="K29" s="364"/>
-      <c r="L29" s="429"/>
+      <c r="J29" s="371"/>
+      <c r="K29" s="371"/>
+      <c r="L29" s="372"/>
     </row>
     <row r="30" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="53"/>
       <c r="B30" s="28">
         <v>4</v>
       </c>
-      <c r="C30" s="386" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" s="376"/>
-      <c r="E30" s="376"/>
-      <c r="F30" s="377"/>
+      <c r="C30" s="373"/>
+      <c r="D30" s="360"/>
+      <c r="E30" s="360"/>
+      <c r="F30" s="361"/>
       <c r="G30" s="53"/>
       <c r="H30" s="28">
         <v>4</v>
       </c>
-      <c r="I30" s="394" t="s">
-        <v>88</v>
-      </c>
-      <c r="J30" s="395"/>
-      <c r="K30" s="395" t="s">
-        <v>74</v>
-      </c>
-      <c r="L30" s="396"/>
+      <c r="I30" s="374" t="s">
+        <v>87</v>
+      </c>
+      <c r="J30" s="375"/>
+      <c r="K30" s="375" t="s">
+        <v>73</v>
+      </c>
+      <c r="L30" s="376"/>
     </row>
     <row r="31" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="55"/>
       <c r="B31" s="56">
         <v>5</v>
       </c>
-      <c r="C31" s="387"/>
-      <c r="D31" s="388"/>
-      <c r="E31" s="388"/>
-      <c r="F31" s="389"/>
+      <c r="C31" s="413"/>
+      <c r="D31" s="414"/>
+      <c r="E31" s="414"/>
+      <c r="F31" s="415"/>
       <c r="G31" s="55"/>
       <c r="H31" s="56">
         <v>5</v>
       </c>
-      <c r="I31" s="378" t="s">
-        <v>155</v>
-      </c>
-      <c r="J31" s="379"/>
-      <c r="K31" s="380" t="s">
-        <v>156</v>
-      </c>
-      <c r="L31" s="381"/>
+      <c r="I31" s="430" t="s">
+        <v>152</v>
+      </c>
+      <c r="J31" s="431"/>
+      <c r="K31" s="382" t="s">
+        <v>153</v>
+      </c>
+      <c r="L31" s="383"/>
     </row>
     <row r="32" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="55"/>
       <c r="B32" s="56">
         <v>6</v>
       </c>
-      <c r="C32" s="403"/>
-      <c r="D32" s="404"/>
-      <c r="E32" s="404"/>
-      <c r="F32" s="405"/>
+      <c r="C32" s="398" t="s">
+        <v>202</v>
+      </c>
+      <c r="D32" s="399"/>
+      <c r="E32" s="399"/>
+      <c r="F32" s="400"/>
       <c r="G32" s="55"/>
       <c r="H32" s="56">
-        <v>7</v>
-      </c>
-      <c r="I32" s="399"/>
-      <c r="J32" s="420"/>
-      <c r="K32" s="420"/>
-      <c r="L32" s="421"/>
+        <v>6</v>
+      </c>
+      <c r="I32" s="398" t="s">
+        <v>203</v>
+      </c>
+      <c r="J32" s="399"/>
+      <c r="K32" s="399"/>
+      <c r="L32" s="400"/>
     </row>
     <row r="33" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="40" t="s">
@@ -6029,118 +6031,118 @@
       <c r="B33" s="26">
         <v>2</v>
       </c>
-      <c r="C33" s="295" t="s">
-        <v>150</v>
-      </c>
-      <c r="D33" s="296"/>
-      <c r="E33" s="296"/>
-      <c r="F33" s="297"/>
+      <c r="C33" s="278" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="279"/>
+      <c r="E33" s="279"/>
+      <c r="F33" s="280"/>
       <c r="G33" s="40" t="s">
         <v>26</v>
       </c>
       <c r="H33" s="26">
         <v>1</v>
       </c>
-      <c r="I33" s="295" t="s">
-        <v>150</v>
-      </c>
-      <c r="J33" s="296"/>
-      <c r="K33" s="296"/>
-      <c r="L33" s="297"/>
+      <c r="I33" s="278" t="s">
+        <v>147</v>
+      </c>
+      <c r="J33" s="279"/>
+      <c r="K33" s="279"/>
+      <c r="L33" s="280"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="77"/>
       <c r="B34" s="28">
         <v>3</v>
       </c>
-      <c r="C34" s="417"/>
-      <c r="D34" s="418"/>
-      <c r="E34" s="418"/>
-      <c r="F34" s="419"/>
+      <c r="C34" s="410"/>
+      <c r="D34" s="411"/>
+      <c r="E34" s="411"/>
+      <c r="F34" s="412"/>
       <c r="G34" s="77"/>
       <c r="H34" s="28">
         <v>2</v>
       </c>
-      <c r="I34" s="406"/>
-      <c r="J34" s="407"/>
-      <c r="K34" s="407"/>
-      <c r="L34" s="408"/>
+      <c r="I34" s="413"/>
+      <c r="J34" s="414"/>
+      <c r="K34" s="414"/>
+      <c r="L34" s="415"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="78"/>
       <c r="B35" s="30">
         <v>4</v>
       </c>
-      <c r="C35" s="415"/>
-      <c r="D35" s="416"/>
-      <c r="E35" s="416"/>
-      <c r="F35" s="402"/>
+      <c r="C35" s="404"/>
+      <c r="D35" s="405"/>
+      <c r="E35" s="405"/>
+      <c r="F35" s="406"/>
       <c r="G35" s="78"/>
       <c r="H35" s="30">
         <v>3</v>
       </c>
-      <c r="I35" s="403"/>
-      <c r="J35" s="404"/>
-      <c r="K35" s="404"/>
-      <c r="L35" s="405"/>
+      <c r="I35" s="407"/>
+      <c r="J35" s="408"/>
+      <c r="K35" s="408"/>
+      <c r="L35" s="409"/>
     </row>
     <row r="36" spans="1:12" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="41"/>
       <c r="B36" s="76"/>
-      <c r="C36" s="422"/>
-      <c r="D36" s="423"/>
-      <c r="E36" s="423"/>
-      <c r="F36" s="424"/>
+      <c r="C36" s="416"/>
+      <c r="D36" s="417"/>
+      <c r="E36" s="417"/>
+      <c r="F36" s="418"/>
       <c r="G36" s="41"/>
       <c r="H36" s="76"/>
-      <c r="I36" s="412"/>
-      <c r="J36" s="413"/>
-      <c r="K36" s="413"/>
-      <c r="L36" s="414"/>
+      <c r="I36" s="401"/>
+      <c r="J36" s="402"/>
+      <c r="K36" s="402"/>
+      <c r="L36" s="403"/>
     </row>
     <row r="37" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="74"/>
       <c r="B37" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="425" t="s">
+      <c r="C37" s="389" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="426"/>
-      <c r="E37" s="426"/>
-      <c r="F37" s="427"/>
+      <c r="D37" s="390"/>
+      <c r="E37" s="390"/>
+      <c r="F37" s="391"/>
       <c r="G37" s="74"/>
       <c r="H37" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="I37" s="425" t="s">
+      <c r="I37" s="389" t="s">
         <v>49</v>
       </c>
-      <c r="J37" s="426"/>
-      <c r="K37" s="426"/>
-      <c r="L37" s="427"/>
+      <c r="J37" s="390"/>
+      <c r="K37" s="390"/>
+      <c r="L37" s="391"/>
     </row>
     <row r="38" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="85" t="s">
         <v>64</v>
       </c>
       <c r="B38" s="86"/>
-      <c r="C38" s="291" t="s">
+      <c r="C38" s="306" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="291"/>
-      <c r="E38" s="291"/>
-      <c r="F38" s="291"/>
+      <c r="D38" s="306"/>
+      <c r="E38" s="306"/>
+      <c r="F38" s="306"/>
       <c r="G38" s="85" t="s">
         <v>64</v>
       </c>
       <c r="H38" s="86"/>
-      <c r="I38" s="291" t="s">
+      <c r="I38" s="306" t="s">
         <v>67</v>
       </c>
-      <c r="J38" s="291"/>
-      <c r="K38" s="291"/>
-      <c r="L38" s="291"/>
+      <c r="J38" s="306"/>
+      <c r="K38" s="306"/>
+      <c r="L38" s="306"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
@@ -6161,17 +6163,77 @@
         <v>55</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>55</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="76">
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="I12:L12"/>
@@ -6188,66 +6250,6 @@
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="I27:L27"/>
     <mergeCell ref="I22:L22"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I18:J18"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="4">
@@ -6319,13 +6321,13 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>11</v>
@@ -6348,11 +6350,11 @@
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G4" s="1"/>
       <c r="L4" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -6378,7 +6380,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="9" t="s">
@@ -6391,7 +6393,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="9" t="s">
@@ -6461,12 +6463,12 @@
       <c r="A9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="428" t="s">
+      <c r="C9" s="392" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="428"/>
-      <c r="E9" s="428"/>
-      <c r="F9" s="428"/>
+      <c r="D9" s="392"/>
+      <c r="E9" s="392"/>
+      <c r="F9" s="392"/>
       <c r="G9" s="11" t="s">
         <v>27</v>
       </c>
@@ -6480,19 +6482,19 @@
       <c r="A10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="214" t="s">
-        <v>105</v>
-      </c>
-      <c r="D10" s="214"/>
+      <c r="C10" s="185" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="185"/>
       <c r="E10" s="66"/>
       <c r="F10" s="66"/>
       <c r="G10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="214" t="s">
-        <v>105</v>
-      </c>
-      <c r="J10" s="214"/>
+      <c r="I10" s="185" t="s">
+        <v>104</v>
+      </c>
+      <c r="J10" s="185"/>
       <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -6528,88 +6530,88 @@
       <c r="B12" s="25">
         <v>2</v>
       </c>
-      <c r="C12" s="360" t="s">
-        <v>167</v>
-      </c>
-      <c r="D12" s="361"/>
-      <c r="E12" s="361"/>
-      <c r="F12" s="362"/>
+      <c r="C12" s="434" t="s">
+        <v>164</v>
+      </c>
+      <c r="D12" s="435"/>
+      <c r="E12" s="435"/>
+      <c r="F12" s="436"/>
       <c r="G12" s="52" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="25">
         <v>4</v>
       </c>
-      <c r="I12" s="464"/>
-      <c r="J12" s="465"/>
-      <c r="K12" s="465"/>
-      <c r="L12" s="466"/>
+      <c r="I12" s="531"/>
+      <c r="J12" s="532"/>
+      <c r="K12" s="532"/>
+      <c r="L12" s="533"/>
     </row>
     <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="27"/>
       <c r="B13" s="28">
         <v>3</v>
       </c>
-      <c r="C13" s="461" t="s">
-        <v>168</v>
-      </c>
-      <c r="D13" s="462"/>
-      <c r="E13" s="462"/>
-      <c r="F13" s="463"/>
+      <c r="C13" s="514" t="s">
+        <v>165</v>
+      </c>
+      <c r="D13" s="515"/>
+      <c r="E13" s="515"/>
+      <c r="F13" s="516"/>
       <c r="G13" s="27"/>
       <c r="H13" s="28">
         <v>5</v>
       </c>
-      <c r="I13" s="458"/>
-      <c r="J13" s="459"/>
-      <c r="K13" s="459"/>
-      <c r="L13" s="460"/>
+      <c r="I13" s="528"/>
+      <c r="J13" s="529"/>
+      <c r="K13" s="529"/>
+      <c r="L13" s="530"/>
     </row>
     <row r="14" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="27"/>
       <c r="B14" s="28">
         <v>4</v>
       </c>
-      <c r="C14" s="461" t="s">
-        <v>169</v>
-      </c>
-      <c r="D14" s="462"/>
-      <c r="E14" s="462"/>
-      <c r="F14" s="463"/>
+      <c r="C14" s="514" t="s">
+        <v>166</v>
+      </c>
+      <c r="D14" s="515"/>
+      <c r="E14" s="515"/>
+      <c r="F14" s="516"/>
       <c r="G14" s="27"/>
       <c r="H14" s="28">
         <v>6</v>
       </c>
-      <c r="I14" s="492" t="s">
-        <v>171</v>
-      </c>
-      <c r="J14" s="493"/>
-      <c r="K14" s="451"/>
-      <c r="L14" s="452"/>
+      <c r="I14" s="463" t="s">
+        <v>168</v>
+      </c>
+      <c r="J14" s="464"/>
+      <c r="K14" s="467"/>
+      <c r="L14" s="468"/>
     </row>
     <row r="15" spans="1:12" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="67"/>
       <c r="B15" s="56">
         <v>5</v>
       </c>
-      <c r="C15" s="526" t="s">
-        <v>181</v>
-      </c>
-      <c r="D15" s="517"/>
-      <c r="E15" s="517" t="s">
-        <v>170</v>
-      </c>
-      <c r="F15" s="518"/>
+      <c r="C15" s="460" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" s="461"/>
+      <c r="E15" s="461" t="s">
+        <v>167</v>
+      </c>
+      <c r="F15" s="462"/>
       <c r="G15" s="68"/>
       <c r="H15" s="30">
         <v>7</v>
       </c>
-      <c r="I15" s="476" t="s">
-        <v>171</v>
-      </c>
-      <c r="J15" s="477"/>
-      <c r="K15" s="478"/>
-      <c r="L15" s="479"/>
+      <c r="I15" s="465" t="s">
+        <v>168</v>
+      </c>
+      <c r="J15" s="466"/>
+      <c r="K15" s="469"/>
+      <c r="L15" s="470"/>
     </row>
     <row r="16" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="22" t="s">
@@ -6618,110 +6620,110 @@
       <c r="B16" s="26">
         <v>3</v>
       </c>
-      <c r="C16" s="464"/>
-      <c r="D16" s="465"/>
-      <c r="E16" s="465"/>
-      <c r="F16" s="466"/>
+      <c r="C16" s="531"/>
+      <c r="D16" s="532"/>
+      <c r="E16" s="532"/>
+      <c r="F16" s="533"/>
       <c r="G16" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H16" s="26">
         <v>2</v>
       </c>
-      <c r="I16" s="464"/>
-      <c r="J16" s="465"/>
-      <c r="K16" s="361" t="s">
-        <v>174</v>
-      </c>
-      <c r="L16" s="362"/>
+      <c r="I16" s="531"/>
+      <c r="J16" s="532"/>
+      <c r="K16" s="435" t="s">
+        <v>171</v>
+      </c>
+      <c r="L16" s="436"/>
     </row>
     <row r="17" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="27"/>
       <c r="B17" s="28">
         <v>4</v>
       </c>
-      <c r="C17" s="467"/>
-      <c r="D17" s="468"/>
-      <c r="E17" s="469" t="s">
-        <v>176</v>
-      </c>
-      <c r="F17" s="470"/>
+      <c r="C17" s="517"/>
+      <c r="D17" s="518"/>
+      <c r="E17" s="519" t="s">
+        <v>204</v>
+      </c>
+      <c r="F17" s="520"/>
       <c r="G17" s="27"/>
       <c r="H17" s="28">
         <v>3</v>
       </c>
-      <c r="I17" s="397"/>
-      <c r="J17" s="398"/>
-      <c r="K17" s="455" t="s">
-        <v>175</v>
-      </c>
-      <c r="L17" s="456"/>
+      <c r="I17" s="423"/>
+      <c r="J17" s="424"/>
+      <c r="K17" s="534" t="s">
+        <v>172</v>
+      </c>
+      <c r="L17" s="535"/>
     </row>
     <row r="18" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="27"/>
       <c r="B18" s="28">
         <v>5</v>
       </c>
-      <c r="C18" s="386" t="s">
-        <v>172</v>
-      </c>
-      <c r="D18" s="376"/>
-      <c r="E18" s="376"/>
-      <c r="F18" s="377"/>
+      <c r="C18" s="373" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="361"/>
       <c r="G18" s="27"/>
       <c r="H18" s="28">
         <v>4</v>
       </c>
-      <c r="I18" s="453" t="s">
-        <v>85</v>
-      </c>
-      <c r="J18" s="454"/>
-      <c r="K18" s="398"/>
-      <c r="L18" s="457"/>
+      <c r="I18" s="450" t="s">
+        <v>84</v>
+      </c>
+      <c r="J18" s="451"/>
+      <c r="K18" s="424"/>
+      <c r="L18" s="536"/>
     </row>
     <row r="19" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="27"/>
       <c r="B19" s="28">
         <v>6</v>
       </c>
-      <c r="C19" s="386" t="s">
-        <v>173</v>
-      </c>
-      <c r="D19" s="376"/>
-      <c r="E19" s="376"/>
-      <c r="F19" s="377"/>
+      <c r="C19" s="373" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19" s="360"/>
+      <c r="E19" s="360"/>
+      <c r="F19" s="361"/>
       <c r="G19" s="27"/>
       <c r="H19" s="28">
         <v>5</v>
       </c>
-      <c r="I19" s="453" t="s">
-        <v>85</v>
-      </c>
-      <c r="J19" s="454"/>
-      <c r="K19" s="451"/>
-      <c r="L19" s="452"/>
+      <c r="I19" s="450" t="s">
+        <v>84</v>
+      </c>
+      <c r="J19" s="451"/>
+      <c r="K19" s="467"/>
+      <c r="L19" s="468"/>
     </row>
     <row r="20" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="29"/>
       <c r="B20" s="30">
         <v>7</v>
       </c>
-      <c r="C20" s="476" t="s">
-        <v>171</v>
-      </c>
-      <c r="D20" s="477"/>
-      <c r="E20" s="478"/>
-      <c r="F20" s="479"/>
+      <c r="C20" s="465" t="s">
+        <v>168</v>
+      </c>
+      <c r="D20" s="466"/>
+      <c r="E20" s="469"/>
+      <c r="F20" s="470"/>
       <c r="G20" s="29"/>
       <c r="H20" s="30">
         <v>6</v>
       </c>
-      <c r="I20" s="384" t="s">
-        <v>171</v>
-      </c>
-      <c r="J20" s="385"/>
-      <c r="K20" s="448"/>
-      <c r="L20" s="449"/>
+      <c r="I20" s="381" t="s">
+        <v>168</v>
+      </c>
+      <c r="J20" s="379"/>
+      <c r="K20" s="377"/>
+      <c r="L20" s="378"/>
     </row>
     <row r="21" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="22" t="s">
@@ -6730,108 +6732,108 @@
       <c r="B21" s="26">
         <v>2</v>
       </c>
-      <c r="C21" s="507"/>
-      <c r="D21" s="508"/>
-      <c r="E21" s="508"/>
-      <c r="F21" s="509"/>
+      <c r="C21" s="493"/>
+      <c r="D21" s="494"/>
+      <c r="E21" s="494"/>
+      <c r="F21" s="495"/>
       <c r="G21" s="22" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="26">
         <v>2</v>
       </c>
-      <c r="I21" s="510" t="s">
-        <v>120</v>
-      </c>
-      <c r="J21" s="511"/>
-      <c r="K21" s="511"/>
-      <c r="L21" s="512"/>
+      <c r="I21" s="496" t="s">
+        <v>118</v>
+      </c>
+      <c r="J21" s="497"/>
+      <c r="K21" s="497"/>
+      <c r="L21" s="498"/>
     </row>
     <row r="22" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="27"/>
       <c r="B22" s="28">
         <v>3</v>
       </c>
-      <c r="C22" s="453" t="s">
-        <v>186</v>
-      </c>
-      <c r="D22" s="454"/>
-      <c r="E22" s="505"/>
-      <c r="F22" s="506"/>
+      <c r="C22" s="450" t="s">
+        <v>182</v>
+      </c>
+      <c r="D22" s="451"/>
+      <c r="E22" s="475"/>
+      <c r="F22" s="476"/>
       <c r="G22" s="27"/>
       <c r="H22" s="28">
         <v>3</v>
       </c>
-      <c r="I22" s="386" t="s">
-        <v>90</v>
-      </c>
-      <c r="J22" s="376"/>
-      <c r="K22" s="376"/>
-      <c r="L22" s="377"/>
+      <c r="I22" s="373" t="s">
+        <v>89</v>
+      </c>
+      <c r="J22" s="360"/>
+      <c r="K22" s="360"/>
+      <c r="L22" s="361"/>
     </row>
     <row r="23" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="27"/>
       <c r="B23" s="28">
         <v>4</v>
       </c>
-      <c r="C23" s="453" t="s">
-        <v>179</v>
-      </c>
-      <c r="D23" s="454"/>
-      <c r="E23" s="505"/>
-      <c r="F23" s="506"/>
+      <c r="C23" s="450" t="s">
+        <v>175</v>
+      </c>
+      <c r="D23" s="451"/>
+      <c r="E23" s="475"/>
+      <c r="F23" s="476"/>
       <c r="G23" s="27"/>
       <c r="H23" s="28">
         <v>4</v>
       </c>
-      <c r="I23" s="406" t="s">
-        <v>83</v>
-      </c>
-      <c r="J23" s="407"/>
-      <c r="K23" s="407"/>
-      <c r="L23" s="408"/>
+      <c r="I23" s="413" t="s">
+        <v>82</v>
+      </c>
+      <c r="J23" s="414"/>
+      <c r="K23" s="414"/>
+      <c r="L23" s="415"/>
     </row>
     <row r="24" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="27"/>
       <c r="B24" s="28">
         <v>5</v>
       </c>
-      <c r="C24" s="453" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" s="454"/>
-      <c r="E24" s="454"/>
-      <c r="F24" s="534"/>
+      <c r="C24" s="450" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="451"/>
+      <c r="E24" s="451"/>
+      <c r="F24" s="452"/>
       <c r="G24" s="27"/>
       <c r="H24" s="28">
         <v>5</v>
       </c>
-      <c r="I24" s="387"/>
-      <c r="J24" s="388"/>
-      <c r="K24" s="376" t="s">
-        <v>182</v>
-      </c>
-      <c r="L24" s="377"/>
+      <c r="I24" s="448"/>
+      <c r="J24" s="449"/>
+      <c r="K24" s="360" t="s">
+        <v>178</v>
+      </c>
+      <c r="L24" s="361"/>
     </row>
     <row r="25" spans="1:12" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="27"/>
       <c r="B25" s="28">
         <v>6</v>
       </c>
-      <c r="C25" s="471"/>
-      <c r="D25" s="472"/>
-      <c r="E25" s="528"/>
-      <c r="F25" s="529"/>
+      <c r="C25" s="521"/>
+      <c r="D25" s="522"/>
+      <c r="E25" s="473"/>
+      <c r="F25" s="474"/>
       <c r="G25" s="27"/>
       <c r="H25" s="28">
         <v>6</v>
       </c>
-      <c r="I25" s="403"/>
-      <c r="J25" s="485"/>
-      <c r="K25" s="535" t="s">
-        <v>182</v>
-      </c>
-      <c r="L25" s="536"/>
+      <c r="I25" s="407"/>
+      <c r="J25" s="453"/>
+      <c r="K25" s="454" t="s">
+        <v>178</v>
+      </c>
+      <c r="L25" s="455"/>
     </row>
     <row r="26" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="22" t="s">
@@ -6840,88 +6842,88 @@
       <c r="B26" s="26">
         <v>2</v>
       </c>
-      <c r="C26" s="473" t="s">
-        <v>177</v>
-      </c>
-      <c r="D26" s="474"/>
-      <c r="E26" s="474"/>
-      <c r="F26" s="475"/>
+      <c r="C26" s="523" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" s="524"/>
+      <c r="E26" s="524"/>
+      <c r="F26" s="525"/>
       <c r="G26" s="22" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="26">
         <v>2</v>
       </c>
-      <c r="I26" s="513" t="s">
-        <v>194</v>
-      </c>
-      <c r="J26" s="514"/>
-      <c r="K26" s="514"/>
-      <c r="L26" s="515"/>
+      <c r="I26" s="481" t="s">
+        <v>189</v>
+      </c>
+      <c r="J26" s="482"/>
+      <c r="K26" s="482"/>
+      <c r="L26" s="483"/>
     </row>
     <row r="27" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="27"/>
       <c r="B27" s="28">
         <v>3</v>
       </c>
-      <c r="C27" s="386" t="s">
-        <v>178</v>
-      </c>
-      <c r="D27" s="376"/>
-      <c r="E27" s="376"/>
-      <c r="F27" s="377"/>
+      <c r="C27" s="373" t="s">
+        <v>174</v>
+      </c>
+      <c r="D27" s="360"/>
+      <c r="E27" s="360"/>
+      <c r="F27" s="361"/>
       <c r="G27" s="27"/>
       <c r="H27" s="28">
         <v>3</v>
       </c>
-      <c r="I27" s="386" t="s">
-        <v>90</v>
-      </c>
-      <c r="J27" s="376"/>
-      <c r="K27" s="376"/>
-      <c r="L27" s="377"/>
+      <c r="I27" s="373" t="s">
+        <v>89</v>
+      </c>
+      <c r="J27" s="360"/>
+      <c r="K27" s="360"/>
+      <c r="L27" s="361"/>
     </row>
     <row r="28" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="27"/>
       <c r="B28" s="28">
         <v>4</v>
       </c>
-      <c r="C28" s="417"/>
-      <c r="D28" s="418"/>
-      <c r="E28" s="521" t="s">
-        <v>183</v>
-      </c>
-      <c r="F28" s="522"/>
+      <c r="C28" s="410"/>
+      <c r="D28" s="411"/>
+      <c r="E28" s="489" t="s">
+        <v>179</v>
+      </c>
+      <c r="F28" s="490"/>
       <c r="G28" s="27"/>
       <c r="H28" s="28">
         <v>4</v>
       </c>
-      <c r="I28" s="492" t="s">
-        <v>195</v>
-      </c>
-      <c r="J28" s="493"/>
-      <c r="K28" s="493"/>
-      <c r="L28" s="523"/>
+      <c r="I28" s="463" t="s">
+        <v>190</v>
+      </c>
+      <c r="J28" s="464"/>
+      <c r="K28" s="464"/>
+      <c r="L28" s="491"/>
     </row>
     <row r="29" spans="1:12" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="29"/>
       <c r="B29" s="30">
         <v>5</v>
       </c>
-      <c r="C29" s="500"/>
-      <c r="D29" s="501"/>
-      <c r="E29" s="519"/>
-      <c r="F29" s="520"/>
+      <c r="C29" s="485"/>
+      <c r="D29" s="486"/>
+      <c r="E29" s="487"/>
+      <c r="F29" s="488"/>
       <c r="G29" s="29"/>
       <c r="H29" s="30">
         <v>5</v>
       </c>
-      <c r="I29" s="500"/>
-      <c r="J29" s="501"/>
-      <c r="K29" s="517" t="s">
-        <v>183</v>
-      </c>
-      <c r="L29" s="518"/>
+      <c r="I29" s="485"/>
+      <c r="J29" s="486"/>
+      <c r="K29" s="461" t="s">
+        <v>179</v>
+      </c>
+      <c r="L29" s="462"/>
     </row>
     <row r="30" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="52" t="s">
@@ -6930,110 +6932,110 @@
       <c r="B30" s="25">
         <v>2</v>
       </c>
-      <c r="C30" s="524"/>
-      <c r="D30" s="382"/>
-      <c r="E30" s="382"/>
-      <c r="F30" s="383"/>
+      <c r="C30" s="492"/>
+      <c r="D30" s="432"/>
+      <c r="E30" s="432"/>
+      <c r="F30" s="433"/>
       <c r="G30" s="22" t="s">
         <v>25</v>
       </c>
       <c r="H30" s="26">
         <v>2</v>
       </c>
-      <c r="I30" s="530" t="s">
-        <v>184</v>
-      </c>
-      <c r="J30" s="531"/>
-      <c r="K30" s="532"/>
-      <c r="L30" s="533"/>
+      <c r="I30" s="477" t="s">
+        <v>180</v>
+      </c>
+      <c r="J30" s="478"/>
+      <c r="K30" s="479"/>
+      <c r="L30" s="480"/>
     </row>
     <row r="31" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="53"/>
       <c r="B31" s="28">
         <v>3</v>
       </c>
-      <c r="C31" s="492" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" s="516"/>
-      <c r="E31" s="376" t="s">
-        <v>191</v>
-      </c>
-      <c r="F31" s="377"/>
+      <c r="C31" s="463" t="s">
+        <v>86</v>
+      </c>
+      <c r="D31" s="484"/>
+      <c r="E31" s="360" t="s">
+        <v>186</v>
+      </c>
+      <c r="F31" s="361"/>
       <c r="G31" s="53"/>
       <c r="H31" s="28">
         <v>3</v>
       </c>
-      <c r="I31" s="386" t="s">
-        <v>184</v>
-      </c>
-      <c r="J31" s="376"/>
-      <c r="K31" s="376" t="s">
-        <v>121</v>
-      </c>
-      <c r="L31" s="377"/>
+      <c r="I31" s="373" t="s">
+        <v>180</v>
+      </c>
+      <c r="J31" s="360"/>
+      <c r="K31" s="360" t="s">
+        <v>119</v>
+      </c>
+      <c r="L31" s="361"/>
     </row>
     <row r="32" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="53"/>
       <c r="B32" s="28">
         <v>4</v>
       </c>
-      <c r="C32" s="484"/>
-      <c r="D32" s="451"/>
-      <c r="E32" s="376" t="s">
-        <v>183</v>
-      </c>
-      <c r="F32" s="377"/>
+      <c r="C32" s="502"/>
+      <c r="D32" s="467"/>
+      <c r="E32" s="360" t="s">
+        <v>179</v>
+      </c>
+      <c r="F32" s="361"/>
       <c r="G32" s="53"/>
       <c r="H32" s="28">
         <v>4</v>
       </c>
-      <c r="I32" s="497" t="s">
-        <v>122</v>
-      </c>
-      <c r="J32" s="527"/>
-      <c r="K32" s="525" t="s">
-        <v>185</v>
-      </c>
-      <c r="L32" s="499"/>
+      <c r="I32" s="471" t="s">
+        <v>120</v>
+      </c>
+      <c r="J32" s="472"/>
+      <c r="K32" s="458" t="s">
+        <v>181</v>
+      </c>
+      <c r="L32" s="459"/>
     </row>
     <row r="33" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="55"/>
       <c r="B33" s="56">
         <v>5</v>
       </c>
-      <c r="C33" s="503"/>
-      <c r="D33" s="504"/>
-      <c r="E33" s="480"/>
-      <c r="F33" s="389"/>
+      <c r="C33" s="456"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="526"/>
+      <c r="F33" s="527"/>
       <c r="G33" s="55"/>
       <c r="H33" s="56">
         <v>5</v>
       </c>
-      <c r="I33" s="503"/>
-      <c r="J33" s="504"/>
-      <c r="K33" s="525" t="s">
-        <v>170</v>
-      </c>
-      <c r="L33" s="499"/>
+      <c r="I33" s="456"/>
+      <c r="J33" s="457"/>
+      <c r="K33" s="458" t="s">
+        <v>167</v>
+      </c>
+      <c r="L33" s="459"/>
     </row>
     <row r="34" spans="1:12" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="57"/>
       <c r="B34" s="30">
         <v>6</v>
       </c>
-      <c r="C34" s="500"/>
-      <c r="D34" s="501"/>
-      <c r="E34" s="501"/>
-      <c r="F34" s="502"/>
+      <c r="C34" s="485"/>
+      <c r="D34" s="486"/>
+      <c r="E34" s="486"/>
+      <c r="F34" s="513"/>
       <c r="G34" s="55"/>
       <c r="H34" s="56">
         <v>6</v>
       </c>
-      <c r="I34" s="403"/>
-      <c r="J34" s="485"/>
-      <c r="K34" s="486"/>
-      <c r="L34" s="487"/>
+      <c r="I34" s="407"/>
+      <c r="J34" s="453"/>
+      <c r="K34" s="503"/>
+      <c r="L34" s="504"/>
     </row>
     <row r="35" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="69" t="s">
@@ -7042,86 +7044,86 @@
       <c r="B35" s="25">
         <v>2</v>
       </c>
-      <c r="C35" s="363" t="s">
-        <v>84</v>
-      </c>
-      <c r="D35" s="364"/>
-      <c r="E35" s="364"/>
-      <c r="F35" s="429"/>
+      <c r="C35" s="370" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="371"/>
+      <c r="E35" s="371"/>
+      <c r="F35" s="372"/>
       <c r="G35" s="40" t="s">
         <v>26</v>
       </c>
       <c r="H35" s="26">
         <v>1</v>
       </c>
-      <c r="I35" s="494"/>
-      <c r="J35" s="495"/>
-      <c r="K35" s="495"/>
-      <c r="L35" s="496"/>
+      <c r="I35" s="509"/>
+      <c r="J35" s="510"/>
+      <c r="K35" s="510"/>
+      <c r="L35" s="511"/>
     </row>
     <row r="36" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="53"/>
       <c r="B36" s="28">
         <v>3</v>
       </c>
-      <c r="C36" s="386" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36" s="376"/>
-      <c r="E36" s="376"/>
-      <c r="F36" s="377"/>
+      <c r="C36" s="373" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="361"/>
       <c r="G36" s="53"/>
       <c r="H36" s="28">
         <v>2</v>
       </c>
-      <c r="I36" s="497" t="s">
-        <v>123</v>
-      </c>
-      <c r="J36" s="498"/>
-      <c r="K36" s="498"/>
-      <c r="L36" s="499"/>
+      <c r="I36" s="471" t="s">
+        <v>121</v>
+      </c>
+      <c r="J36" s="512"/>
+      <c r="K36" s="512"/>
+      <c r="L36" s="459"/>
     </row>
     <row r="37" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="70"/>
       <c r="B37" s="28">
         <v>4</v>
       </c>
-      <c r="C37" s="492"/>
-      <c r="D37" s="493"/>
-      <c r="E37" s="376" t="s">
-        <v>119</v>
-      </c>
-      <c r="F37" s="377"/>
+      <c r="C37" s="463"/>
+      <c r="D37" s="464"/>
+      <c r="E37" s="360" t="s">
+        <v>117</v>
+      </c>
+      <c r="F37" s="361"/>
       <c r="G37" s="55"/>
       <c r="H37" s="28">
         <v>3</v>
       </c>
-      <c r="I37" s="497" t="s">
-        <v>123</v>
-      </c>
-      <c r="J37" s="498"/>
-      <c r="K37" s="498"/>
-      <c r="L37" s="499"/>
+      <c r="I37" s="471" t="s">
+        <v>121</v>
+      </c>
+      <c r="J37" s="512"/>
+      <c r="K37" s="512"/>
+      <c r="L37" s="459"/>
     </row>
     <row r="38" spans="1:12" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="71"/>
       <c r="B38" s="30">
         <v>5</v>
       </c>
-      <c r="C38" s="488"/>
-      <c r="D38" s="489"/>
-      <c r="E38" s="490" t="s">
-        <v>119</v>
-      </c>
-      <c r="F38" s="491"/>
+      <c r="C38" s="505"/>
+      <c r="D38" s="506"/>
+      <c r="E38" s="507" t="s">
+        <v>117</v>
+      </c>
+      <c r="F38" s="508"/>
       <c r="G38" s="64"/>
       <c r="H38" s="30">
         <v>4</v>
       </c>
-      <c r="I38" s="481"/>
-      <c r="J38" s="482"/>
-      <c r="K38" s="482"/>
-      <c r="L38" s="483"/>
+      <c r="I38" s="499"/>
+      <c r="J38" s="500"/>
+      <c r="K38" s="500"/>
+      <c r="L38" s="501"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
@@ -7143,13 +7145,13 @@
         <v>55</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>55</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.4">
@@ -7163,11 +7165,72 @@
     </row>
   </sheetData>
   <mergeCells count="87">
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="C30:F30"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="K33:L33"/>
     <mergeCell ref="C15:D15"/>
@@ -7184,72 +7247,11 @@
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="I30:J30"/>
     <mergeCell ref="K30:L30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K25:L25"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="6">
